--- a/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46913088-D537-4078-95E5-E39E7097012C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44A570C-343D-49F1-B641-DE2991D1FC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1260" windowWidth="36060" windowHeight="19710" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1125" yWindow="1125" windowWidth="36330" windowHeight="19485" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -799,12 +799,6 @@
     <t>percent</t>
   </si>
   <si>
-    <t>t co2e/t grain sold</t>
-  </si>
-  <si>
-    <t>t co2e/t baled hay/silage</t>
-  </si>
-  <si>
     <t>Economic emissions assignment</t>
   </si>
   <si>
@@ -1265,6 +1259,12 @@
   </si>
   <si>
     <t>Manure used as feed on own farm</t>
+  </si>
+  <si>
+    <t>t co2e/t liveweight sold</t>
+  </si>
+  <si>
+    <t>t co2e/t manure sold</t>
   </si>
 </sst>
 </file>
@@ -3467,7 +3467,7 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3497,7 +3497,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <font>
@@ -12083,7 +12083,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{E2CA7C24-2440-47BC-8296-4E06A1997FD6}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{642394F7-56DA-41DB-A6DF-4604D42201F6}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{93AD8A04-E6ED-452A-BA77-CD86A87A2623}" name="Sale date" dataDxfId="51"/>
+    <tableColumn id="2" xr3:uid="{93AD8A04-E6ED-452A-BA77-CD86A87A2623}" name="Sale date" dataDxfId="41"/>
     <tableColumn id="3" xr3:uid="{FD3BC078-BDA8-41B1-A38C-5D070201A63B}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{BCCD5BF7-9608-4DD4-83C7-D6C023152096}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{6625426D-1AE8-4F66-AC8B-2F50B438E4A1}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -12320,8 +12320,8 @@
     <tableColumn id="2" xr3:uid="{8628A244-7FCA-4923-B809-B69CE86B5CDE}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{FAD9C63D-6E32-48F0-8A23-222E15F46B11}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{5EDBE82F-7B3C-458A-8638-8F86879CF287}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="50"/>
-    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="49"/>
+    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="50"/>
     <tableColumn id="7" xr3:uid="{A201D4C4-5F18-4228-8444-52A30734BB16}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12338,8 +12338,8 @@
     <tableColumn id="2" xr3:uid="{0E7A6865-A484-4EA8-BE54-5D641629A627}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{3E8C7762-D226-4D20-9E9C-87D78E3C44EB}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{4BFD5FBC-8263-4629-836C-DDA0F8DB50DF}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="48"/>
-    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="47"/>
+    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="49"/>
+    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="48"/>
     <tableColumn id="7" xr3:uid="{5C3D4C29-1D29-4869-8E15-91152F19AFCD}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12356,8 +12356,8 @@
     <tableColumn id="2" xr3:uid="{F15C1AF3-5D79-4EFF-A7BC-85CD71AF8BCF}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{E627CA70-3484-4F31-AEDF-45A8D9B88D5B}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{17EAABE4-C534-43AF-A841-58EDEBD26AB6}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="46"/>
-    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="47"/>
+    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="46"/>
     <tableColumn id="7" xr3:uid="{399918FC-2F3F-431B-90D1-3CF016CF6FB7}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12374,8 +12374,8 @@
     <tableColumn id="2" xr3:uid="{BC53EBA0-F074-453F-8CEB-CA1F6ECC908D}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{443C80E7-5900-4A26-A586-B5571F50B9F7}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{C01B1081-DB35-4821-8766-E86DBB122E80}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="45"/>
+    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="44"/>
     <tableColumn id="7" xr3:uid="{6CAA4E36-3A57-4A0B-8F59-4A9A9900E954}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12392,8 +12392,8 @@
     <tableColumn id="2" xr3:uid="{4E3BAE35-86E5-4F71-98DC-491AD05B9B47}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{27B2AE81-8632-4140-9460-9C99650189CD}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{9C973ECC-975D-44BC-8B9B-BFC0C605F944}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="42"/>
-    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="41"/>
+    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="42"/>
     <tableColumn id="7" xr3:uid="{73A8FFE4-648C-4FC3-BBE0-724E1B5D1A5A}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12756,7 +12756,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="91" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D1" s="91"/>
       <c r="E1" s="91"/>
@@ -12812,7 +12812,7 @@
         <v>1</v>
       </c>
       <c r="D6" s="78" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12849,7 +12849,7 @@
     <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E9" s="1" t="e" cm="1">
         <f t="array" ref="E9">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
@@ -12879,7 +12879,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E10" s="1" t="e" cm="1">
         <f t="array" ref="E10">VEERG_4_5_1_1__1_TotalAnnualMethaneEmissions_Result_Method1</f>
@@ -12910,7 +12910,7 @@
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E11" s="1" t="e" cm="1">
         <f t="array" ref="E11">VEERG_4_5_1_3__1_TotalAnnualDirectNitrousOxideEmissionsFromMMS_Result_Method1</f>
@@ -12941,7 +12941,7 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E12" s="1" t="e" cm="1">
         <f t="array" ref="E12">VEERG_4_5_1_5__1_AnnualAtmosphericDepositionEmissionsFromMMS_Result_Method1</f>
@@ -12972,7 +12972,7 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E13" s="1" t="e" cm="1">
         <f t="array" ref="E13">VEERG_4_5_1_7__1_AnnualEmissionsFromLeachingAndRunoffFromMMS_Result_Method1</f>
@@ -13185,7 +13185,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E20" s="1" t="e" cm="1">
         <f t="array" ref="E20">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope1_Result_Method1</f>
@@ -13196,7 +13196,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="H20" s="1" t="e">
         <f>E20</f>
@@ -13238,13 +13238,13 @@
     <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="78" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="12" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>9</v>
@@ -13293,7 +13293,7 @@
     </row>
     <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="86" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="E28" s="87"/>
       <c r="F28" s="87"/>
@@ -13314,13 +13314,13 @@
     <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="78" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="12" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>9</v>
@@ -13341,7 +13341,7 @@
     </row>
     <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E34" s="1" t="e" cm="1">
         <f t="array" ref="E34">VEERG_15_1_1_1__1_EmissionsFromPurchasedLivestock_Pigs_Result_Method1</f>
@@ -13368,7 +13368,7 @@
     </row>
     <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E35" s="1" t="e" cm="1">
         <f t="array" ref="E35">VEERG_15_2_1_1__1_EmissionsFromPurchasedFeed_Result_Method1</f>
@@ -13395,7 +13395,7 @@
     </row>
     <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="E36" s="1" t="e" cm="1">
         <f t="array" ref="E36">VEERG_15_7_1_1__1_EmissionsFromPurchasedServices_Result_Method1</f>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E37" s="1" t="e" cm="1">
         <f t="array" ref="E37">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_CleaningChemicals_Result_Method1</f>
@@ -13449,7 +13449,7 @@
     </row>
     <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E38" s="1" t="e" cm="1">
         <f t="array" ref="E38">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_PharmacyChemicals_Result_Method1</f>
@@ -13476,7 +13476,7 @@
     </row>
     <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E39" s="1" t="e" cm="1">
         <f t="array" ref="E39">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_Uncategorised_Result_Method1</f>
@@ -13503,7 +13503,7 @@
     </row>
     <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E40" s="1" t="e" cm="1">
         <f t="array" ref="E40">VEERG_15_11_1_1__1_TotalUpstreamEmissionsFromFuel_Result</f>
@@ -13558,7 +13558,7 @@
     </row>
     <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E42" s="1" t="e" cm="1">
         <f t="array" ref="E42">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope3_Result_Method1</f>
@@ -13585,7 +13585,7 @@
     </row>
     <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E43" s="1" t="e" cm="1">
         <f t="array" ref="E43">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Incoming_Result_Method1</f>
@@ -13612,7 +13612,7 @@
     </row>
     <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E44" s="1" t="e" cm="1">
         <f t="array" ref="E44">VEERG_15_14_1_1__1_EmbeddedEmissionsFromUpstreamFreight_Outgoing_Result_Method1</f>
@@ -13639,7 +13639,7 @@
     </row>
     <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="86" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E45" s="87"/>
       <c r="F45" s="87"/>
@@ -13667,7 +13667,7 @@
     <row r="49" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="86" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E50" s="87">
         <f>SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise])</f>
@@ -13698,7 +13698,7 @@
     </row>
     <row r="56" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="95" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E56" s="93" t="e">
         <f>Result_Enterprise_Scope1_Method1+Result_Enterprise_Scope2_Method1+Result_Enterprise_Scope3_Method1</f>
@@ -13709,12 +13709,12 @@
         <v>#NAME?</v>
       </c>
       <c r="G56" s="94" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="57" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="95" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E57" s="93" t="e">
         <f>Result_Enterprise_Gross_Method1-Result_Enterprise_Removals</f>
@@ -13725,7 +13725,7 @@
         <v>#NAME?</v>
       </c>
       <c r="G57" s="94" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="58" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13786,7 +13786,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="C1" s="91" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -13824,7 +13824,7 @@
     </row>
     <row r="36" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D36" s="76" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E36" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Gross_Method1</f>
@@ -13840,7 +13840,7 @@
     </row>
     <row r="37" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D37" s="76" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="E37" s="1" t="e">
         <f>Result_EmissionsForWholeProductionCycle_Net_Method1</f>
@@ -13862,7 +13862,7 @@
     </row>
     <row r="42" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D42" s="78" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="4:10" x14ac:dyDescent="0.25">
@@ -13876,7 +13876,7 @@
         <v>118</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>120</v>
@@ -13890,18 +13890,18 @@
     </row>
     <row r="44" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F44" s="1">
         <f>X_Cell_Enterprise_LiveweightSold</f>
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="G44" s="1">
         <f>F44/(F44+F46)</f>
-        <v>0.99980003999200162</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H44" s="1" t="e">
         <f>(E36/F44)*G44</f>
@@ -13912,23 +13912,23 @@
         <v>#NAME?</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
     </row>
     <row r="45" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F45" s="1">
         <f>F44</f>
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="G45" s="1">
         <f>G44</f>
-        <v>0.99980003999200162</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H45" s="1" t="e">
         <f>(E37/F45)*G45</f>
@@ -13939,12 +13939,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
     </row>
     <row r="46" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>124</v>
@@ -13955,7 +13955,7 @@
       </c>
       <c r="G46" s="1">
         <f>F46/(F44+F46)</f>
-        <v>1.9996000799840031E-4</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H46" s="1" t="e">
         <f>(E36/F46)*G46</f>
@@ -13966,12 +13966,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="47" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>124</v>
@@ -13982,7 +13982,7 @@
       </c>
       <c r="G47" s="1">
         <f>G46</f>
-        <v>1.9996000799840031E-4</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="H47" s="97" t="e">
         <f>(E37/F47)*G47</f>
@@ -13993,12 +13993,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="48" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>126</v>
@@ -14020,7 +14020,7 @@
     </row>
     <row r="50" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
       <c r="D50" s="78" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.25">
@@ -14034,13 +14034,13 @@
         <v>118</v>
       </c>
       <c r="G51" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="H51" s="12" t="s">
-        <v>146</v>
-      </c>
       <c r="I51" s="12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="J51" s="12" t="s">
         <v>119</v>
@@ -14048,14 +14048,14 @@
     </row>
     <row r="52" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F52" s="1">
         <f>X_Cell_Enterprise_LiveweightSold</f>
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="G52" s="1">
         <f>X_Cell_Enterprise_PercentIncomeFromLiveweightSold</f>
@@ -14070,19 +14070,19 @@
         <v>#NAME?</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
     </row>
     <row r="53" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D53" s="1" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>123</v>
       </c>
       <c r="F53" s="1">
         <f>F52</f>
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="G53" s="1">
         <f>G52</f>
@@ -14097,12 +14097,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>142</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>124</v>
@@ -14124,12 +14124,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="55" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>124</v>
@@ -14151,12 +14151,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>143</v>
+        <v>297</v>
       </c>
     </row>
     <row r="56" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D56" s="1" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>126</v>
@@ -15119,11 +15119,11 @@
     </row>
     <row r="22" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D22" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E22" s="77">
-        <f>SUM(Table_Input_LivestockSales[Total liveweight sold])</f>
-        <v>5000</v>
+        <f>SUM(Table_Input_LivestockSales[Total liveweight sold])*10^-3</f>
+        <v>5</v>
       </c>
       <c r="F22" s="17" t="s">
         <v>20</v>
@@ -15131,7 +15131,7 @@
     </row>
     <row r="23" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D23" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E23" s="75">
         <v>10</v>
@@ -15142,7 +15142,7 @@
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="E24" s="19">
         <v>0.1</v>
@@ -15153,7 +15153,7 @@
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E25" s="19">
         <v>0.1</v>
@@ -15164,7 +15164,7 @@
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E27" s="19">
         <v>0.8</v>
@@ -15175,7 +15175,7 @@
     </row>
     <row r="28" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E28" s="19">
         <v>0.2</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D31" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="34" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -15197,16 +15197,16 @@
     </row>
     <row r="36" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D36" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>231</v>
+      </c>
+      <c r="F36" s="20" t="s">
         <v>232</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="G36" s="79" t="s">
         <v>233</v>
-      </c>
-      <c r="F36" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="G36" s="79" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.25">
@@ -15220,7 +15220,7 @@
     </row>
     <row r="41" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D41" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="43" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
@@ -15237,7 +15237,7 @@
     </row>
     <row r="46" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="48" spans="4:7" x14ac:dyDescent="0.25">
@@ -15548,7 +15548,7 @@
   <sheetData>
     <row r="1" spans="3:13" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C1" s="11" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="2" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15568,33 +15568,33 @@
     <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="88" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="F6" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="G6" s="20" t="s">
         <v>263</v>
       </c>
-      <c r="F6" s="20" t="s">
+      <c r="H6" s="20" t="s">
         <v>264</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="I6" s="20" t="s">
         <v>265</v>
-      </c>
-      <c r="H6" s="20" t="s">
-        <v>266</v>
-      </c>
-      <c r="I6" s="20" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="34"/>
       <c r="E7" s="14" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="F7" s="98">
         <v>45566</v>
@@ -15772,7 +15772,7 @@
   <sheetData>
     <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
       <c r="C1" s="11" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
@@ -15791,30 +15791,30 @@
     </row>
     <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="7" spans="3:13" x14ac:dyDescent="0.25">
       <c r="D7" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="E7" s="79" t="s">
+      <c r="G7" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F7" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G7" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="H7" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="I7" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J7" s="79" t="s">
         <v>151</v>
-      </c>
-      <c r="I7" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="J7" s="79" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="8" spans="3:13" x14ac:dyDescent="0.25">
@@ -15823,13 +15823,13 @@
         <v>Liveweight sold</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H8" s="83"/>
       <c r="I8" s="83"/>
@@ -15844,13 +15844,13 @@
         <v>Manure produced</v>
       </c>
       <c r="E9" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H9" s="83"/>
       <c r="I9" s="83"/>
@@ -15865,13 +15865,13 @@
         <v>Manure sold</v>
       </c>
       <c r="E10" s="14" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H10" s="83"/>
       <c r="I10" s="83"/>
@@ -15886,13 +15886,13 @@
         <v>Percent income from liveweight sold</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H11" s="83"/>
       <c r="I11" s="83"/>
@@ -15907,13 +15907,13 @@
         <v>Percent income from manure sold</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H12" s="83"/>
       <c r="I12" s="83"/>
@@ -15930,30 +15930,30 @@
     </row>
     <row r="15" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D15" s="2" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="17" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D17" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E17" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="F17" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="E17" s="79" t="s">
+      <c r="G17" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F17" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G17" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="H17" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="I17" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J17" s="79" t="s">
         <v>151</v>
-      </c>
-      <c r="I17" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="J17" s="79" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="18" spans="4:10" x14ac:dyDescent="0.25">
@@ -15962,13 +15962,13 @@
         <v>Leaching zone</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H18" s="83"/>
       <c r="I18" s="83"/>
@@ -15983,13 +15983,13 @@
         <v>Elevation</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H19" s="83"/>
       <c r="I19" s="83"/>
@@ -16004,13 +16004,13 @@
         <v>Average temperature for reporting period</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H20" s="83"/>
       <c r="I20" s="83"/>
@@ -16025,13 +16025,13 @@
         <v>Total rainfall for reporting period</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H21" s="83"/>
       <c r="I21" s="83"/>
@@ -16046,13 +16046,13 @@
         <v>Potential evapotranspiration for reporting period</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H22" s="83"/>
       <c r="I22" s="83"/>
@@ -16067,13 +16067,13 @@
         <v>Number of frost days for reporting period</v>
       </c>
       <c r="E23" s="85" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F23" s="85" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G23" s="85" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H23" s="83"/>
       <c r="I23" s="83"/>
@@ -16090,44 +16090,44 @@
     </row>
     <row r="26" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D28" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E28" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="F28" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="E28" s="79" t="s">
+      <c r="G28" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F28" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G28" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="H28" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="I28" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J28" s="79" t="s">
         <v>151</v>
-      </c>
-      <c r="I28" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="J28" s="79" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="29" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D29" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H29" s="83"/>
       <c r="I29" s="83"/>
@@ -16138,7 +16138,7 @@
     </row>
     <row r="30" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D30" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -16152,16 +16152,16 @@
     </row>
     <row r="31" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D31" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H31" s="83"/>
       <c r="I31" s="83"/>
@@ -16172,16 +16172,16 @@
     </row>
     <row r="32" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D32" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H32" s="83"/>
       <c r="I32" s="83"/>
@@ -16192,16 +16192,16 @@
     </row>
     <row r="33" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D33" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H33" s="83"/>
       <c r="I33" s="83"/>
@@ -16212,7 +16212,7 @@
     </row>
     <row r="34" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
@@ -16226,7 +16226,7 @@
     </row>
     <row r="35" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
@@ -16246,30 +16246,30 @@
     </row>
     <row r="38" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D38" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D40" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E40" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="F40" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="E40" s="79" t="s">
+      <c r="G40" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F40" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G40" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="H40" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="I40" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J40" s="79" t="s">
         <v>151</v>
-      </c>
-      <c r="I40" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="J40" s="79" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="41" spans="4:10" x14ac:dyDescent="0.25">
@@ -16278,13 +16278,13 @@
         <v>Fuel purchases</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G41" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H41" s="83"/>
       <c r="I41" s="83"/>
@@ -16299,13 +16299,13 @@
         <v>Fuel consumption</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G42" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H42" s="83"/>
       <c r="I42" s="83"/>
@@ -16320,13 +16320,13 @@
         <v>Electricity consumption</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G43" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H43" s="83"/>
       <c r="I43" s="83"/>
@@ -16341,13 +16341,13 @@
         <v>Electricity generation</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H44" s="83"/>
       <c r="I44" s="83"/>
@@ -16364,30 +16364,30 @@
     </row>
     <row r="48" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D48" s="2" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="50" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D50" s="79" t="s">
+        <v>221</v>
+      </c>
+      <c r="E50" s="79" t="s">
+        <v>222</v>
+      </c>
+      <c r="F50" s="79" t="s">
         <v>223</v>
       </c>
-      <c r="E50" s="79" t="s">
+      <c r="G50" s="79" t="s">
         <v>224</v>
       </c>
-      <c r="F50" s="79" t="s">
-        <v>225</v>
-      </c>
-      <c r="G50" s="79" t="s">
-        <v>226</v>
-      </c>
       <c r="H50" s="79" t="s">
+        <v>149</v>
+      </c>
+      <c r="I50" s="79" t="s">
+        <v>150</v>
+      </c>
+      <c r="J50" s="79" t="s">
         <v>151</v>
-      </c>
-      <c r="I50" s="79" t="s">
-        <v>152</v>
-      </c>
-      <c r="J50" s="79" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="51" spans="4:10" x14ac:dyDescent="0.25">
@@ -16396,13 +16396,13 @@
         <v>Farm input purchases</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="H51" s="83"/>
       <c r="I51" s="83"/>
@@ -16417,13 +16417,13 @@
         <v>Inbound freight use</v>
       </c>
       <c r="E52" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H52" s="83"/>
       <c r="I52" s="83"/>
@@ -16438,13 +16438,13 @@
         <v>Outbound freight use</v>
       </c>
       <c r="E53" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H53" s="83"/>
       <c r="I53" s="83"/>
@@ -16455,7 +16455,7 @@
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -16473,13 +16473,13 @@
         <v>Solid waste generation and treatment</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G55" s="14" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H55" s="83"/>
       <c r="I55" s="83"/>
@@ -16496,7 +16496,7 @@
     </row>
     <row r="59" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
       <c r="D59" s="86" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E59" s="87" t="str">
         <f>(J14+J25+J37+J46+J57)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
@@ -20650,39 +20650,39 @@
     </row>
     <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D263" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="264" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D264" s="1" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="265" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D265" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E265" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F265" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G265" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V265" s="1"/>
       <c r="BN265" s="22"/>
     </row>
     <row r="266" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D266" s="20" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E266" s="20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F266" s="20" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G266" s="20">
         <v>5</v>
@@ -20692,13 +20692,13 @@
     </row>
     <row r="267" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D267" s="20" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E267" s="20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F267" s="20" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G267" s="20">
         <v>4</v>
@@ -20708,13 +20708,13 @@
     </row>
     <row r="268" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D268" s="20" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E268" s="20" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F268" s="20" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G268" s="20">
         <v>3</v>
@@ -20724,13 +20724,13 @@
     </row>
     <row r="269" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D269" s="20" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E269" s="20" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F269" s="20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G269" s="20">
         <v>2</v>
@@ -20740,13 +20740,13 @@
     </row>
     <row r="270" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D270" s="20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E270" s="20" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F270" s="20" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G270" s="20">
         <v>1</v>
@@ -20756,34 +20756,34 @@
     </row>
     <row r="273" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D273" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="274" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D274" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E274" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F274" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G274" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V274" s="1"/>
       <c r="BN274" s="22"/>
     </row>
     <row r="275" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D275" s="20" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E275" s="20" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F275" s="20" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="G275" s="20">
         <v>5</v>
@@ -20793,13 +20793,13 @@
     </row>
     <row r="276" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D276" s="20" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E276" s="20" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F276" s="20" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="G276" s="20">
         <v>4</v>
@@ -20809,13 +20809,13 @@
     </row>
     <row r="277" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D277" s="20" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E277" s="20" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F277" s="20" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="G277" s="20">
         <v>3</v>
@@ -20825,13 +20825,13 @@
     </row>
     <row r="278" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D278" s="20" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="E278" s="20" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F278" s="20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="G278" s="20">
         <v>2</v>
@@ -20841,13 +20841,13 @@
     </row>
     <row r="279" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D279" s="20" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E279" s="20" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F279" s="20" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="G279" s="20">
         <v>1</v>
@@ -20857,34 +20857,34 @@
     </row>
     <row r="282" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D282" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="283" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D283" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E283" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F283" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G283" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V283" s="1"/>
       <c r="BN283" s="22"/>
     </row>
     <row r="284" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D284" s="20" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E284" s="20" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F284" s="20" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G284" s="20">
         <v>5</v>
@@ -20894,13 +20894,13 @@
     </row>
     <row r="285" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D285" s="20" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="E285" s="20" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F285" s="20" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G285" s="20">
         <v>4</v>
@@ -20910,13 +20910,13 @@
     </row>
     <row r="286" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D286" s="20" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E286" s="20" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F286" s="20" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G286" s="20">
         <v>3</v>
@@ -20926,13 +20926,13 @@
     </row>
     <row r="287" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D287" s="20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E287" s="20" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F287" s="20" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G287" s="20">
         <v>2</v>
@@ -20942,13 +20942,13 @@
     </row>
     <row r="288" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D288" s="20" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E288" s="20" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F288" s="20" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G288" s="20">
         <v>1</v>
@@ -20958,34 +20958,34 @@
     </row>
     <row r="291" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D291" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="292" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D292" s="20" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="E292" s="20" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F292" s="20" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G292" s="20" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="V292" s="1"/>
       <c r="BN292" s="22"/>
     </row>
     <row r="293" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D293" s="20" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E293" s="20" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="F293" s="20" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G293" s="20">
         <v>5</v>
@@ -20995,13 +20995,13 @@
     </row>
     <row r="294" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D294" s="20" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E294" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F294" s="20" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G294" s="20">
         <v>4</v>
@@ -21011,13 +21011,13 @@
     </row>
     <row r="295" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D295" s="20" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E295" s="20" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F295" s="20" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G295" s="20">
         <v>3</v>
@@ -21027,13 +21027,13 @@
     </row>
     <row r="296" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D296" s="20" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="E296" s="20" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F296" s="20" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G296" s="20">
         <v>2</v>
@@ -21043,13 +21043,13 @@
     </row>
     <row r="297" spans="4:66" x14ac:dyDescent="0.25">
       <c r="D297" s="20" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="E297" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F297" s="20" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="G297" s="20">
         <v>1</v>
@@ -21087,6 +21087,30 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100ACB660BB23738846A00119B5826AC974" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3e3613359d4ae7f6bda6c57be713f101">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7291119c-fce9-4911-96ae-b800be5dccd8" xmlns:ns3="09eef6d6-daa8-4301-8f9f-b1ec38079286" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="87491bfad7f11426ad96486e70428b3e" ns2:_="" ns3:_="">
     <xsd:import namespace="7291119c-fce9-4911-96ae-b800be5dccd8"/>
@@ -21281,31 +21305,34 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{809E3D44-A88D-4EBF-A307-6B8CE77A3361}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -21322,31 +21349,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9A9CF321-0D35-4044-BC72-33748FE2B865}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\htdocs\zneagcrc\GAF-VEERG-Functions\Excel\Enterprises\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D44A570C-343D-49F1-B641-DE2991D1FC83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB9B97B5-88DF-463C-B610-64EC3A308197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="1125" windowWidth="36330" windowHeight="19485" activeTab="2" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
+    <workbookView xWindow="1350" yWindow="720" windowWidth="36330" windowHeight="19485" activeTab="6" xr2:uid="{992023F3-CAB7-4E5B-A348-08D563A0EF40}"/>
   </bookViews>
   <sheets>
     <sheet name="Home" sheetId="71" r:id="rId1"/>
@@ -317,7 +317,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="290">
   <si>
     <t>Home</t>
   </si>
@@ -1178,30 +1178,6 @@
   </si>
   <si>
     <t>Manure produced</t>
-  </si>
-  <si>
-    <t>Head count</t>
-  </si>
-  <si>
-    <t>Volatile solid production</t>
-  </si>
-  <si>
-    <t>Nitrogen in waste</t>
-  </si>
-  <si>
-    <t>Duration of stay</t>
-  </si>
-  <si>
-    <t>Production and manure management systems</t>
-  </si>
-  <si>
-    <t>Livestock sales</t>
-  </si>
-  <si>
-    <t>Livestock purchases</t>
-  </si>
-  <si>
-    <t>Use of contractors and service providers</t>
   </si>
   <si>
     <t>Swine management</t>
@@ -3467,7 +3443,7 @@
       </fill>
     </dxf>
     <dxf>
-      <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
+      <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -3497,7 +3473,7 @@
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="171" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     </dxf>
     <dxf>
       <font>
@@ -12083,7 +12059,7 @@
   <tableColumns count="6">
     <tableColumn id="6" xr3:uid="{E2CA7C24-2440-47BC-8296-4E06A1997FD6}" name="Transaction name" dataCellStyle="Input text"/>
     <tableColumn id="1" xr3:uid="{642394F7-56DA-41DB-A6DF-4604D42201F6}" name="Class (select)" dataCellStyle="Input select"/>
-    <tableColumn id="2" xr3:uid="{93AD8A04-E6ED-452A-BA77-CD86A87A2623}" name="Sale date" dataDxfId="41"/>
+    <tableColumn id="2" xr3:uid="{93AD8A04-E6ED-452A-BA77-CD86A87A2623}" name="Sale date" dataDxfId="51"/>
     <tableColumn id="3" xr3:uid="{FD3BC078-BDA8-41B1-A38C-5D070201A63B}" name="Head sold"/>
     <tableColumn id="4" xr3:uid="{BCCD5BF7-9608-4DD4-83C7-D6C023152096}" name="Average weight per head (kg)"/>
     <tableColumn id="5" xr3:uid="{6625426D-1AE8-4F66-AC8B-2F50B438E4A1}" name="Total liveweight sold" dataCellStyle="Input number general calculated">
@@ -12320,8 +12296,8 @@
     <tableColumn id="2" xr3:uid="{8628A244-7FCA-4923-B809-B69CE86B5CDE}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{FAD9C63D-6E32-48F0-8A23-222E15F46B11}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{5EDBE82F-7B3C-458A-8638-8F86879CF287}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="51"/>
-    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="50"/>
+    <tableColumn id="5" xr3:uid="{58811FFB-FE3A-4DD8-BE53-E8CB588BCB77}" name="Notes" dataDxfId="50"/>
+    <tableColumn id="6" xr3:uid="{1219F6AC-7C79-4EDD-8C55-F7A78277AE3F}" name="Evidence files" dataDxfId="49"/>
     <tableColumn id="7" xr3:uid="{A201D4C4-5F18-4228-8444-52A30734BB16}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Enterprise[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12338,8 +12314,8 @@
     <tableColumn id="2" xr3:uid="{0E7A6865-A484-4EA8-BE54-5D641629A627}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{3E8C7762-D226-4D20-9E9C-87D78E3C44EB}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{4BFD5FBC-8263-4629-836C-DDA0F8DB50DF}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="49"/>
-    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="48"/>
+    <tableColumn id="5" xr3:uid="{E8075AB8-A4A6-48D2-A746-36F9CD68017F}" name="Notes" dataDxfId="48"/>
+    <tableColumn id="6" xr3:uid="{73F97399-8A3B-4EFB-9481-CBD7CB1C44EB}" name="Evidence files" dataDxfId="47"/>
     <tableColumn id="7" xr3:uid="{5C3D4C29-1D29-4869-8E15-91152F19AFCD}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_Site[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12356,8 +12332,8 @@
     <tableColumn id="2" xr3:uid="{F15C1AF3-5D79-4EFF-A7BC-85CD71AF8BCF}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{E627CA70-3484-4F31-AEDF-45A8D9B88D5B}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{17EAABE4-C534-43AF-A841-58EDEBD26AB6}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="47"/>
-    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="46"/>
+    <tableColumn id="5" xr3:uid="{179CA6A6-4732-423D-BA28-31ED41FEC488}" name="Notes" dataDxfId="46"/>
+    <tableColumn id="6" xr3:uid="{865FA280-4A36-4101-BD09-20356916B4D5}" name="Evidence files" dataDxfId="45"/>
     <tableColumn id="7" xr3:uid="{399918FC-2F3F-431B-90D1-3CF016CF6FB7}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_PastureManagement[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12374,8 +12350,8 @@
     <tableColumn id="2" xr3:uid="{BC53EBA0-F074-453F-8CEB-CA1F6ECC908D}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{443C80E7-5900-4A26-A586-B5571F50B9F7}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{C01B1081-DB35-4821-8766-E86DBB122E80}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="45"/>
-    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{A1104D67-6CCD-4845-87B4-822F83200DD9}" name="Notes" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{690D112F-6792-478E-99EE-B77B520B2164}" name="Evidence files" dataDxfId="43"/>
     <tableColumn id="7" xr3:uid="{6CAA4E36-3A57-4A0B-8F59-4A9A9900E954}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FuelElectricity[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12392,8 +12368,8 @@
     <tableColumn id="2" xr3:uid="{4E3BAE35-86E5-4F71-98DC-491AD05B9B47}" name="When was the data sourced?" dataCellStyle="Input select"/>
     <tableColumn id="3" xr3:uid="{27B2AE81-8632-4140-9460-9C99650189CD}" name="Where is the data sourced from?" dataCellStyle="Input select"/>
     <tableColumn id="4" xr3:uid="{9C973ECC-975D-44BC-8B9B-BFC0C605F944}" name="How much of the data was from direct samples?" dataCellStyle="Input select"/>
-    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{F255A018-D1E3-4FA7-9B50-4726EC2E2E56}" name="Notes" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{16D79CDB-80AA-4F28-B5E0-282205F97C41}" name="Evidence files" dataDxfId="41"/>
     <tableColumn id="7" xr3:uid="{73A8FFE4-648C-4FC3-BBE0-724E1B5D1A5A}" name="Score" dataCellStyle="Input number general calculated">
       <calculatedColumnFormula>IFERROR(_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[When was the data sourced?]],Table_SourceData_DataQuality_TemporalRepresentativeness[User friendly description],Table_SourceData_DataQuality_TemporalRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[Where is the data sourced from?]],Table_SourceData_DataQuality_SpatialRepresentativeness[User friendly description],Table_SourceData_DataQuality_SpatialRepresentativeness[Score])+_xlfn.XLOOKUP(Table_Input_DataQuality_FarmInputsFreightWaste[[#This Row],[How much of the data was from direct samples?]],Table_SourceData_DataQuality_SampleSize[User friendly description],Table_SourceData_DataQuality_SampleSize[Score]), 0)</calculatedColumnFormula>
     </tableColumn>
@@ -12849,7 +12825,7 @@
     <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E9" s="1" t="e" cm="1">
         <f t="array" ref="E9">VEERG_3_5_1_1__1_TotalAnnualMethaneFromEntericFermentation_Result_Method1</f>
@@ -12879,7 +12855,7 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E10" s="1" t="e" cm="1">
         <f t="array" ref="E10">VEERG_4_5_1_1__1_TotalAnnualMethaneEmissions_Result_Method1</f>
@@ -12910,7 +12886,7 @@
         <v>4.2.1.1-2 Methane</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="E11" s="1" t="e" cm="1">
         <f t="array" ref="E11">VEERG_4_5_1_3__1_TotalAnnualDirectNitrousOxideEmissionsFromMMS_Result_Method1</f>
@@ -12941,7 +12917,7 @@
         <v>4.2.1.3-4 Soil direct N2O</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E12" s="1" t="e" cm="1">
         <f t="array" ref="E12">VEERG_4_5_1_5__1_AnnualAtmosphericDepositionEmissionsFromMMS_Result_Method1</f>
@@ -12972,7 +12948,7 @@
         <v>4.2.1.5-6 Soil atm. deposition</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="E13" s="1" t="e" cm="1">
         <f t="array" ref="E13">VEERG_4_5_1_7__1_AnnualEmissionsFromLeachingAndRunoffFromMMS_Result_Method1</f>
@@ -13185,7 +13161,7 @@
         <v>Acknowledgements</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="E20" s="1" t="e" cm="1">
         <f t="array" ref="E20">VEERG_10_1_1_1__1_EmissionsFromWasteManagement_Scope1_Result_Method1</f>
@@ -13341,7 +13317,7 @@
     </row>
     <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="E34" s="1" t="e" cm="1">
         <f t="array" ref="E34">VEERG_15_1_1_1__1_EmissionsFromPurchasedLivestock_Pigs_Result_Method1</f>
@@ -13368,7 +13344,7 @@
     </row>
     <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="E35" s="1" t="e" cm="1">
         <f t="array" ref="E35">VEERG_15_2_1_1__1_EmissionsFromPurchasedFeed_Result_Method1</f>
@@ -13449,7 +13425,7 @@
     </row>
     <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="E38" s="1" t="e" cm="1">
         <f t="array" ref="E38">VEERG_15_10_1_1__1_OtherPurchasedGoodsAndServices_PharmacyChemicals_Result_Method1</f>
@@ -13890,7 +13866,7 @@
     </row>
     <row r="44" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>123</v>
@@ -13912,12 +13888,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J44" s="10" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="45" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D45" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>123</v>
@@ -13939,12 +13915,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J45" s="10" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="46" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D46" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>124</v>
@@ -13966,12 +13942,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J46" s="10" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="47" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D47" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>124</v>
@@ -13993,12 +13969,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J47" s="10" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="48" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D48" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>126</v>
@@ -14048,7 +14024,7 @@
     </row>
     <row r="52" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D52" s="1" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>123</v>
@@ -14070,12 +14046,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J52" s="10" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D53" s="1" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>123</v>
@@ -14097,12 +14073,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J53" s="10" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D54" s="1" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>124</v>
@@ -14124,12 +14100,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J54" s="10" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="55" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D55" s="1" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>124</v>
@@ -14151,12 +14127,12 @@
         <v>#NAME?</v>
       </c>
       <c r="J55" s="10" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="56" spans="4:10" x14ac:dyDescent="0.25">
       <c r="D56" s="1" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>126</v>
@@ -15142,7 +15118,7 @@
     </row>
     <row r="24" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D24" s="1" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="E24" s="19">
         <v>0.1</v>
@@ -15153,7 +15129,7 @@
     </row>
     <row r="25" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D25" s="1" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="E25" s="19">
         <v>0.1</v>
@@ -15164,7 +15140,7 @@
     </row>
     <row r="27" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="E27" s="19">
         <v>0.8</v>
@@ -15175,7 +15151,7 @@
     </row>
     <row r="28" spans="4:6" x14ac:dyDescent="0.25">
       <c r="D28" s="1" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="E28" s="19">
         <v>0.2</v>
@@ -15756,7 +15732,7 @@
   <sheetPr>
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
-  <dimension ref="C1:M59"/>
+  <dimension ref="C1:M58"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -16090,7 +16066,7 @@
     </row>
     <row r="26" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
     </row>
     <row r="28" spans="4:10" x14ac:dyDescent="0.25">
@@ -16117,8 +16093,9 @@
       </c>
     </row>
     <row r="29" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D29" s="1" t="s">
-        <v>269</v>
+      <c r="D29" s="1" t="str">
+        <f>"Head count"</f>
+        <v>Head count</v>
       </c>
       <c r="E29" s="14" t="s">
         <v>200</v>
@@ -16137,8 +16114,9 @@
       </c>
     </row>
     <row r="30" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D30" s="1" t="s">
-        <v>272</v>
+      <c r="D30" s="1" t="str">
+        <f>"Duration of stay"</f>
+        <v>Duration of stay</v>
       </c>
       <c r="E30" s="14"/>
       <c r="F30" s="14"/>
@@ -16151,8 +16129,9 @@
       </c>
     </row>
     <row r="31" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D31" s="1" t="s">
-        <v>270</v>
+      <c r="D31" s="1" t="str">
+        <f>"Volatile solid production"</f>
+        <v>Volatile solid production</v>
       </c>
       <c r="E31" s="14" t="s">
         <v>200</v>
@@ -16171,8 +16150,9 @@
       </c>
     </row>
     <row r="32" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D32" s="1" t="s">
-        <v>271</v>
+      <c r="D32" s="1" t="str">
+        <f>"Nitrogen in waste"</f>
+        <v>Nitrogen in waste</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>200</v>
@@ -16191,8 +16171,9 @@
       </c>
     </row>
     <row r="33" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D33" s="1" t="s">
-        <v>273</v>
+      <c r="D33" s="1" t="str">
+        <f>"Production and manure management systems"</f>
+        <v>Production and manure management systems</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>200</v>
@@ -16211,8 +16192,9 @@
       </c>
     </row>
     <row r="34" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D34" s="1" t="s">
-        <v>274</v>
+      <c r="D34" s="1" t="str">
+        <f>"Livestock sales"</f>
+        <v>Livestock sales</v>
       </c>
       <c r="E34" s="14"/>
       <c r="F34" s="14"/>
@@ -16225,8 +16207,9 @@
       </c>
     </row>
     <row r="35" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D35" s="1" t="s">
-        <v>275</v>
+      <c r="D35" s="1" t="str">
+        <f>"Livestock purchases"</f>
+        <v>Livestock purchases</v>
       </c>
       <c r="E35" s="14"/>
       <c r="F35" s="14"/>
@@ -16454,8 +16437,9 @@
       </c>
     </row>
     <row r="54" spans="4:10" x14ac:dyDescent="0.25">
-      <c r="D54" s="1" t="s">
-        <v>276</v>
+      <c r="D54" s="1" t="str">
+        <f>"Use of contractors and service providers"</f>
+        <v>Use of contractors and service providers</v>
       </c>
       <c r="E54" s="14"/>
       <c r="F54" s="14"/>
@@ -16494,11 +16478,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="59" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="D59" s="86" t="s">
+    <row r="58" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
+      <c r="D58" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="E59" s="87" t="str">
+      <c r="E58" s="87" t="str">
         <f>(J14+J25+J37+J46+J57)&amp;" out of "&amp;((COUNT(Table_Input_DataQuality_Enterprise[Score])*15)+(COUNT(Table_Input_DataQuality_Site[Score])*15)+(COUNT(Table_Input_DataQuality_PastureManagement[Score])*15)+(COUNT(Table_Input_DataQuality_FuelElectricity[Score])*15)+(COUNT(Table_Input_DataQuality_FarmInputsFreightWaste[Score])*15))</f>
         <v>293 out of 405</v>
       </c>
@@ -21087,7 +21071,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21100,14 +21091,7 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="09eef6d6-daa8-4301-8f9f-b1ec38079286" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7291119c-fce9-4911-96ae-b800be5dccd8">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBOADIATwAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAE4AMgBPADoAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABOADIATwApAFwAbgBHAFcAUABOADIATwA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8ATgAyAE8ALAAgAEcAVwBQAF8ATgAyAE8ALABcAG4AIAAgACAAIABFAF8ATgAyAE8AIAAqACAARwBXAFAAXwBOADIATwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBOADIATwB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBOADIATwB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUATgAyAE8AXAAiACwAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ARQBDAEgANAAgAEMATwAyAGUAXABuAHQAIABDAE8AMgBlAFwAbgBFAEMASAA0ADoAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAoAHQAIABDAEgANAApAFwAbgBHAFcAUABDAEgANAA6ACAAZwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIAAoAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEMASAA0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAF8AQwBIADQALAAgAEcAVwBQAF8AQwBIADQALABcAG4AIAAgACAAIABFAF8AQwBIADQAIAAqACAARwBXAFAAXwBDAEgANABcAG4AIAAgACkAXABuADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMAbwBuAHYAZQByAHQAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAB0AG8AIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIABlAHEAdQBpAHYAYQBsAGUAbgB0ACAAZQBtAGkAcwBzAGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBlAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEMATwAyAF8AZQAgAD0AIABFAF8AewBDAEgANAB9ACAAXABcAHQAaQBtAGUAcwAgAEcAVwBQAF8AewBDAEgANAB9AFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBIADQAXAAiACwAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAEMASAA0AFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAUgBPAFcAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAApACAAKwAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAIAAtACAAMQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAAsAFwAbgAgACAAQwBPAEwAVQBNAE4AKABUAGEAYgBsAGUASABlAGEAZABlAHIAQwBlAGwAbAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgAEEAcgByAGEAeQBEAGEAdABhACwAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAsACAAWwBDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5AF0ALABcAG4AIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIABJAE4ARABFAFgAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAVQBOAEkAUQBVAEUAKABBAHIAcgBhAHkARABhAHQAYQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBPAFcAKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwALAAgAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEMATwBMAFUATQBOACgAKQAtAFUAdABpAGwAaQB0AHkAXwBHAGUAdABBAHIAcgBhAHkAVABhAGIAbABlAEMAbwBsAHUAbQBuAFMAdABhAHIAdABOAHUAbQBiAGUAcgAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAKQAsACAAMQAsACAAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACAAIAAgACAAKQAsACAAXAAiAFwAIgBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFwAIgBcACIAKQBcAG4AIAAgACAAIAApACwAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApACwAIAAwACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBUAHcAbwBDAG8AbAB1AG0AbgBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlADEALAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADIALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAWwBWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQBdACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQApACoAKABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACwAIABcACIAXAAiACwAIABWAGEAbAB1AGUASQBGAEYAYQBsAHMAZQApACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAxACwAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMgAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAFsAVgBhAGwAdQBlAEkAZgBGAGEAbABzAGUAXQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUAMQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ADEALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAyACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkALAAgAFwAIgBcACIALAAgAFYAYQBsAHUAZQBJAGYARgBhAGwAcwBlACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEMAcgBpAHQAZQByAGkAYQAxACwAIABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACwAIABbAE0AdQBsAHQAaQBwAGwAaQBlAHIAXQAsACAAWwBDAHIAaQB0AGUAcgBpAGEAMgBdACwAWwBDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAHUAbAB0AGkAcABsAGkAZQByACwAIABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsADEALABNAHUAbAB0AGkAcABsAGkAZQByACkALABcAG4AIAAgACAAIABxAHUAYQBuAHQAaQB0AHkALAAgAFEAdQBhAG4AdABpAHQAeQAqAE0AdQBsAHQAaQBwAGwAaQBlAHIALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADEAKQAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAyACwASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABDAHIAaQB0AGUAcgBpAGEAMgApACwAMQAsAC0ALQAoAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAyACkAKQAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABjAHIAaQB0AGUAcgBpAGEAMQAqAGMAcgBpAHQAZQByAGkAYQAyACoAcQB1AGEAbgB0AGkAdAB5ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwAgAFMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQAgAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAHMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAUwAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgACAAIAAgACAARQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAXABuACAAIAAgACAAIAAgACAAIABtACwATQBPAE4AVABIACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABkACwARABBAFkAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALAAgAC8AKgBoAGUAbABwAGUAcgA6ACAAZQBuAGQAIABkAGEAdABlACAAZgBvAHIAIABhACAAcgBlAHAAbwByAHQAaQBuAGcAIABwAGUAcgBpAG8AZAAgAHMAdABhAHIAdABpAG4AZwAgAGEAdAAgAGEAIABnAGkAdgBlAG4AIABkAGEAdABlACoALwBcAG4AIAAgACAAIAAgACAAIAAgAFAAZQByAGkAbwBkAEUAbgBkACwATABBAE0AQgBEAEEAKABzAHQALABFAEQAQQBUAEUAKABzAHQALAAxADIAKQAtADEAKQAsACAALwAqAG8AbgBsAHkAIABuAGUAZQBkACAAdABvACAAbABvAG8AawAgAGIAYQBjAGsAIAAzADYANQAgAGQAYQB5AHMAKABtAGEAeAAgAG8AdgBlAHIAbABhAHAAIAB3AGkAbgBkAG8AdwApACoALwBcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGEAIABlAG4AZABzACAAYgBlAGYAbwByAGUAIABTACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABuAGUAeAB0ACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjAFMAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYgAgAHMAdABhAHIAdABzACAAYQBmAHQAZQByACAARQAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAcAByAGUAdgBpAG8AdQBzACAAeQBlAGEAcgAqAC8AXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlAEUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAbgAsAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AHIAcwAsAFMARQBRAFUARQBOAEMARQAoAG4ALAAxACwAZgBpAHIAcwB0AFkAZQBhAHIALAAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzACwARABBAFQARQAoAHkAcgBzACwAbQAsAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwAsAE0AQQBQACgAcwB0AGEAcgB0AHMALABQAGUAcgBpAG8AZABFAG4AZAApACwAXABuACAAIAAgACAAIAAgACAAIAB0AGEAZwAsAEkARgAoAHMAdABhAHIAdABzAD0AUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAIgAgACgAVABoAGkAcwAgAHIAZQBwAG8AcgB0AGkAbgBnACAAYwB5AGMAbABlACkAXAAiACwAXAAiAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAHMAdABhAHIAdABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZQBuAGQAcwBUAGUAeAB0ACwAVABFAFgAVAAoAGUAbgBkAHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABuAD0AMAAsAFwAIgBcACIALABIAFMAVABBAEMASwAoAHMAdABhAHIAdABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAFwAIgAgAHQAbwAgAFwAIgAgAFwAdQAwADAAMgA2ACAAZQBuAGQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIAB0AGEAZwApACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuAD0ATABBAE0AQgBEAEEAKABGAHUAbgBjAHQAaQBvAG4ALAAgAFQARQBYAFQAQgBFAEYATwBSAEUAKABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQAsACAAXAAiACgAXAAiACkAKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5ACwAIABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkAEEAcgByAGEAeQAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5ACwAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAEkARgAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAPQBcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEEAbgB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAgAD0AIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKAAxACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEEAcgByAGEAeQA9AFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5AD0ASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAQQByAHIAYQB5AD0AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAKQAsACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALABcAG4AIAAgACAAIABTAHQAYQB0AGUAQwBvAG0AbQBvAG4ATgBhAG0AZQBBAHIAcgBhAHkALAAgAFMAdABhAHQAZQBBAGIAYgByAGUAdgBpAGEAdABpAG8AbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUALAAgAFMAdABhAHQAZQBDAG8AbQBtAG8AbgBOAGEAbQBlAEEAcgByAGEAeQAsACAAUwB0AGEAdABlAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUASAB5AHAAZQByAGwAaQBuAGsAXABuAD0ATABBAE0AQgBEAEEAKABUAGEAcgBnAGUAdABDAGUAbABsACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAHMAaAAsACAAVABFAFgAVABBAEYAVABFAFIAKABDAEUATABMACgAXAAiAGYAaQBsAGUAbgBhAG0AZQBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsACAAXAAiAF0AXAAiACkALABcAG4AIAAgACAAIABhAGQAZAByACwAIABDAEUATABMACgAXAAiAGEAZABkAHIAZQBzAHMAXAAiACwAIABUAGEAcgBnAGUAdABDAGUAbABsACkALABcAG4AIAAgACAAIABcACIAIwBcAHUAMAAwADIANwBcACIAIABcAHUAMAAwADIANgAgAHMAaAAgAFwAdQAwADAAMgA2ACAAXAAiAFwAdQAwADAAMgA3ACEAXAAiACAAXAB1ADAAMAAyADYAIABhAGQAZAByAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdABcAG4APQBMAEEATQBCAEQAQQAoAFQAYQByAGcAZQB0AEMAZQBsAGwALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAcwBoACwAIABUAEUAWABUAEEARgBUAEUAUgAoAEMARQBMAEwAKABcACIAZgBpAGwAZQBuAGEAbQBlAFwAIgAsACAAVABhAHIAZwBlAHQAQwBlAGwAbAApACwAIABcACIAXQBcACIAKQAsAFwAbgAgACAAIAAgAGEAZABkAHIALAAgAEMARQBMAEwAKABcACIAYQBkAGQAcgBlAHMAcwBcACIALAAgAFQAYQByAGcAZQB0AEMAZQBsAGwAKQAsAFwAbgAgACAAIAAgAFwAIgAjAFwAIgAgAFwAdQAwADAAMgA2ACAAYQBkAGQAcgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMQBfADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAxACwAIAAyACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgBnAHUAbQBlAG4AdABzAF8AMwBfADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAHIAZwB1AG0AZQBuAHQAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIABDAEgATwBPAFMARQBDAE8ATABTACgAQQByAGcAdQBtAGUAbgB0AHMAQQByAHIAYQB5ACwAIAAzACwAIAA0ACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8ARwBlAHQATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUALAAgAE0ATQBTACwAIABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACwAIABNAE0AUwBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAIAAgAE0ARQBEAEkAQQBOACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFIATwBVAE4ARAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQAsACAAMAApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATQBJAE4AKABUAGUAbQBwAGUAcgBhAHQAdQByAGUAQQByAHIAYQB5ACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABNAEEAWAAoAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAFgATABPAE8ASwBVAFAAKABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFIAZQBzAHUAbAB0AHMASQB0AGUAbQBGAHIAbwBtAEUAcQB1AGEAdABpAG8AbgBUAGkAdABsAGUAQQBuAGQAUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGkAdABsAGUAQwBlAGwAbAAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAAsAFwAbgAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABMAEUARgBUACgAUwBvAHUAcgBjAGUAQwBlAGwAbAAsACAARgBJAE4ARAAoAFwAIgAsAFwAIgAsACAAUwBvAHUAcgBjAGUAQwBlAGwAbAApACAALQAxACkALAAgAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABcACIALAAgAFwAIgBcACIAKQAgAFwAdQAwADAAMgA2ACAAXAAiACAAXAAiACAAXAB1ADAAMAAyADYAIABUAGkAdABsAGUAQwBlAGwAbABcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsADAALgAyADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABcAG4ANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXABuAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AZwBlAG4AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoANQAuADUALgAyAC4AMwAgAEMAbwBuAHMAdABhAG4AdAAgAFAAYQByAGEAbQBlAHQAZQByAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBCAF8AMQAwAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAMAAuADAAMQAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXABuAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQAgACgARQBGAE4AMgBPACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqAFwAIgAsAFwAIgBFAEYATgAyAE8AXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAbwBuAGwAeQBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAAiACwAIABcACIAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAANQA5ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsADAALgAwADAANwAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsADAALgAwADAAMQA4ACwAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEwAbwB3ACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBIAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcAAgACgAbABvAHcAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADIAOQAsACAAXAAiAEMAcgBvAHAAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAKQBcACIALAAwAC4AMAAwADgALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByAFwAIgAsADAALgAwADEAOQA5ACwAIABcACIAUwB1AGcAYQByAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAwAC4AMAAwADUAMwAsACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAYQBsACAAYwByAG8AcABzAFwAIgAsADAALgAwADAANgA0ACwAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAYwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwApAFwAIgAsADAALgAwADAAMwAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAQwBvAG4AdABpAG4AdQBvAHUAcwAgAGYAbABvAG8AZABpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQAgACgAcwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwApAFwAIgAsADAALgAwADAANQAsACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABhAG4AZAAgAG0AdQBsAHQAaQBwAGwAZQAgAGQAcgBhAGkAbgBhAGcAZQAsACAAbwByACAAYQBsAHQAZQByAG4AYQB0AGUAIAB3AGUAdAB0AGkAbgBnACAAYQBuAGQAIABkAHIAeQBpAG4AZwBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsADAALgAwADAAMgA2ACwAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBGAG8AcgBlAHMAdAByAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAZAB1AHAAbABpAGMAYQB0AGUAIABcAHUAMAAwADIANwBBAHEAdQBhAGMAdQBsAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbQBvAHYAZQBkACAAYQBzAHQAZQByAGkAcwBrAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AGkAcgByAGkAZwBhAHQAaQBvAG4AIABtAGUAdABoAG8AZABcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBuAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcAHUAMAAwADIANwAgAHIAbwB3ACAAdwBpAHQAaAAgAHMAYQBtAGUAIABFAEYAIABmAG8AcgAgAGwAbwB3ACAAYQBuAGQAIABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAFwAbgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAbgBJAFAAQwBDADoAIABOADIATwAgAEUATQBJAFMAUwBJAE8ATgBTACAARgBSAE8ATQAgAE0AQQBOAEEARwBFAEQAIABTAE8ASQBMAFMALAAgAEEATgBEACAAQwBPADIAIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABMAEkATQBFACAAQQBOAEQAIABVAFIARQBBACAAQQBQAFAATABJAEMAQQBUAEkATwBOAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwBXAEUAVAAgAGYAbwByACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAEMAaABhAHAAdABlAHIAIAAxACwAIABzAGUAYwB0AGkAbwBuACAAMQAuADgALgAyACAATABlAGEAYwBoAGkAbgBnACwAIABjAGwAaQBtAGEAdABlACAAYQBuAGQAIAByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBJAFAAQwBDACAAMgAwADEAOQAgAFIAZQBmAGkAbgBlAG0AZQBuAHQAIABWAG8AbAB1AG0AZQAgADQAOgAgAEMAaABhAHAAdABlAHIAIAAxADEAOgAgAE4AMgBPACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATQBhAG4AYQBnAGUAZAAgAFMAbwBpAGwAcwAsACAAYQBuAGQAIABDAE8AMgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAEwAaQBtAGUAIABhAG4AZAAgAFUAcgBlAGEAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAVABhAGIAbABlACAAYwByAGUAYQB0AGUAZAAgAGIAYQBzAGUAZAAgAG8AbgAgAFYARQBFAFIARwAgAHQAZQB4AHQAIABcAHUAMAAwADIANwBBAHIAZQBhAHMAIABhAHIAZQAgAHMAdQBiAGoAZQBjAHQAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIAAoAGkALgBlAC4ALAAgAGkAbgAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQApACAAdwBoAGUAbgAuAC4ALgAgAHQAaABlACAAbABhAG4AZAAgAGkAcwAgAGkAcgByAGkAZwBhAHQAZQBkACAAKABlAHgAYwBlAHAAdAAgAGQAcgBpAHAAIABpAHIAcgBpAGcAYQB0AGkAbwBuACkALgBcAHUAMAAwADIANwBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAyADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBQAFIAUAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABvAHIAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AMgBPACAALQAgAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAyAC4AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAEUARgBQAFIAUABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgAsACAAMAAuADAAMAAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABDAGgAYQBuAGcAZQBkACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzAFwAdQAwADAAMgA3ACAAdABvACAAcwBpAG4AZwB1AGwAYQByACAAXAB1ADAAMAAyADcARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAHUAMAAwADIANwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG8AbgB0AGgAcwAgAHQAbwAgAFMAZQBhAHMAbwBuAHMAIABNAGEAcABwAGkAbgBnAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AdABoAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBKAGEAbgB1AGEAcgB5AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGUAYgByAHUAYQByAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQByAGMAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBwAHIAaQBsAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AG4AZQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASgB1AGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQB1AGcAdQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBwAHQAZQBtAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAGMAdABvAGIAZQByAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdgBlAG0AYgBlAHIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBjAGUAbQBiAGUAcgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAEMARgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAG4AdQByAGUAIABNAGEAbgBhAGcAZQBtAGUAbgB0ACAAEyAgAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABwAGUAcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIAAoAGYAcgBhAGMAdABpAG8AbgApACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AOAAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AQwBGAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAFwAIgAsACAAXAAiAE0AQQBUACAAKAC6AEMAKQBcACIALAAgAFwAIgBVAG4AYwBvAHYAZQByAGUAZAAgAGEAbgBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAFMAbAB1AHIAcgB5ACAAKAB3AGkAdABoAG8AdQB0ACAAbgBhAHQAdQByAGEAbAAgAGMAcgB1AHMAdAApAFwAIgAsACAAXAAiAEQAYQBpAGwAeQAgAHMAcAByAGUAYQBkACAAKABiACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAUwB0AG8AcgBhAGcAZQAgAFwAdQAwADAAMwBjADEAIABtAG8AbgB0AGgAXAAiACwAIABcACIARABlAGUAcAAgAEwAaQB0AHQAZQByAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQAgACgAdwBpAHQAaAAvAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwAgAGkAbgB0AG8AIABwAGUAbABsAGUAdABpAHoAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIABcACIAUABhAHMAdAB1AHIAZQAsACAAUgBhAG4AZwBlACAAYQBuAGQAIABQAGEAZABkAG8AYwBrACAAKABjACkAKABkACkAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgAFwAIgBkIjEAMABcACIALAAgADAALgA2ADYALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIAAxADEALAAgADAALgA2ADgALAAgADAALgAxACwAIAAwAC4AMQAxACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMgAsACAAMAAuADcALAAgADAALgAxACwAIAAwAC4AMQAzACwAIAAwAC4AMAAwADEALAAgADAALgAwADAANQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbABcACIALAAgADEAMwAsACAAMAAuADcAMQAsACAAMAAuADEALAAgADAALgAxADQALAAgADAALgAwADAAMQAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbwBsAFwAIgAsACAAMQA0ACwAIAAwAC4ANwAzACwAIAAwAC4AMQAsACAAMAAuADEANQAsACAAMAAuADAAMAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMQA1ACwAIAAwAC4ANwA0ACwAIAAwAC4AMQAsACAAMAAuADEANwAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEANgAsACAAMAAuADcANQAsACAAMAAuADEALAAgADAALgAxADgALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADcALAAgADAALgA3ADYALAAgADAALgAxACwAIAAwAC4AMgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADEAOAAsACAAMAAuADcANwAsACAAMAAuADEALAAgADAALgAyADIALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAxADkALAAgADAALgA3ADcALAAgADAALgAxACwAIAAwAC4AMgA0ACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAwACwAIAAwAC4ANwA4ACwAIAAwAC4AMQAsACAAMAAuADIANgAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIAMQAsACAAMAAuADcAOAAsACAAMAAuADEALAAgADAALgAyADkALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADIALAAgADAALgA3ADgALAAgADAALgAxACwAIAAwAC4AMwAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAZQBtAHAAZQByAGEAdABlAFwAIgAsACAAMgAzACwAIAAwAC4ANwA5ACwAIAAwAC4AMQAsACAAMAAuADMANAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAbQBwAGUAcgBhAHQAZQBcACIALAAgADIANAAsACAAMAAuADcAOQAsACAAMAAuADEALAAgADAALgAzADcALAAgADAALgAwADAANQAsACAAMAAuADAAMQAsACAAMAAuADAAMgAsACAAMAAuADAAMwAsACAAMAAuADAANAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALAAgADAALAAgADAALgAwADAANAA3ACwAIAAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIAAyADUALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAAxACwAIAAwAC4AMAAwADUALAAgADAALgAwADEALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADYALAAgADAALgA3ADkALAAgADAALgAxACwAIAAwAC4ANAA0ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxADUALAAgADAALgAwADIALAAgADAALgAwADMALAAgADAALgAwADQALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwACwAIAAwACwAIAAwAC4AMAAwADQANwAsACAAMgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AXAAiACwAIAAyADcALAAgADAALgA4ACwAIAAwAC4AMQAsACAAMAAuADQAOAAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtAFwAIgAsACAAXAAiAGUiMgA4AFwAIgAsACAAMAAuADgALAAgADAALgAxACwAIAAwAC4ANQAsACAAMAAuADAAMQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAyACwAIAAwAC4AMAAzACwAIAAwAC4AMAA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAsACAAMAAsACAAMAAuADAAMAA0ADcALAAgADIAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIALAAgAFwAIgBMAGkAcQB1AGkAZAAgAHMAeQBzAHQAZQBtAHMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGIAZQBkAGQAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIATQBBAFQAIAByAGEAdwBcACIAIABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBDAEYAVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAHIAbwB3ACAAbwBmACAATgBJAFIAIABNAE0AQQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgAgAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAdwBpAHQAaAAgAGEAbgBkACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAAcwBlAHAAYQByAGEAdABlACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBNAEEAVAAgAHIAYQB3AFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGwAbABvAHcAIABsAG8AbwBrAHUAcAAgAG8AZgAgAG4AdQBtAGIAZQByAHMALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAbgBkAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBGAE4AaQAgAFwAdQAwADAAMgA2ACAARQBGAE4AMgBPAGkAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBuAGQAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4ANABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgAFwAIgBFAEYATgBpACAAXAB1ADAAMAAyADYAIABFAEYATgAyAE8AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiACwAIAAwAC4AMAAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAG4AZABDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9AF0ALAAiAHAAcgBvAGoAZQBjAHQATgBhAG0AZQBzACIAOgBbACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAUgBvAHcAUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEQAaQBzAHAAbABhAHkAQQByAHIAYQB5AEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUAVAB3AG8AQwBvAGwAdQBtAG4AcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBPAG4AZQBDAG8AbAB1AG0AbgBBAG4AZABIAGUAYQBkAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAE4AMgBPAEUARgBGAHIAbwBtAFAAcgBvAGQASQByAHIAaQBnAGEAdABpAG8AbgBSAGEAaQBuAGYAYQBsAGwAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEMAbwBuAHYAZQByAHQAUwB0AGEAdABlAEMAbwBtAG0AbwBuAE4AYQBtAGUAVABvAEEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlAEgAeQBwAGUAcgBsAGkAbgBrAEQAaQBmAGYAZQByAGUAbgB0AFMAaABlAGUAdAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBSAGUAcwB1AGwAdABzAEkAdABlAG0ARgByAG8AbQBFAHEAdQBhAHQAaQBvAG4AVABpAHQAbABlAEEAbgBkAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYATgAyAE8AXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAFAAYQBzAHQAdQByAGUAUgBhAG4AZwBlAEEAbgBkAFAAYQBkAGQAbwBjAGsAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBQAGEAcwB0AHUAcgBlAFIAYQBuAGcAZQBBAG4AZABQAGEAZABkAG8AYwBrAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAUABhAHMAdAB1AHIAZQBSAGEAbgBnAGUAQQBuAGQAUABhAGQAZABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBNAG8AbgB0AGgAcwBUAG8AUwBlAGEAcwBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATQBvAG4AdABoAHMAVABvAFMAZQBhAHMAbwBuAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE0AbwBuAHQAaABzAFQAbwBTAGUAYQBzAG8AbgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgBdACwAIgBsAG8AYwBhAGwAZQAiADoAewAiAGwAaQBzAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgByAG8AdwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgA7ACIALAAiAGMAbwBsAHUAbQBuAFMAZQBwAGEAcgBhAHQAbwByACIAOgAiACwAIgAsACIAdABoAG8AdQBzAGEAbgBkAHMAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBQAG8AcwBpAHQAaQBvAG4AcwAiADoAWwAzAF0ALAAiAGQAZQBjAGkAbQBhAGwAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALgAiACwAIgBkAGEAdABlAE8AcgBkAGUAcgAiADoAIgBEAE0AWQAiACwAIgBjAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwAIgA6ACIAJAAiACwAIgBpAHMAQwB1AHIAcgBlAG4AYwB5AFMAeQBtAGIAbwBsAEwAZQBhAGQAIgA6AHQAcgB1AGUALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwBlAHAAQgB5AFMAcABhAGMAZQAiADoAZgBhAGwAcwBlACwAIgByAG8AdwBMAGUAdAB0AGUAcgAiADoAIgBSACIALAAiAGMAbwBsAHUAbQBuAEwAZQB0AHQAZQByACIAOgAiAEMAIgAsACIAcgBjAEwAZQBmAHQAQgByAGEAYwBrAGUAdAAiADoAIgBbACIALAAiAHIAYwBSAGkAZwBoAHQAQgByAGEAYwBrAGUAdAAiADoAIgBdACIALAAiAHMAdABhAHQAZQBtAGUAbgB0AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAbABvAGMAYQBsAGUATgBhAG0AZQAiADoAIgBlAG4ALQB1AHMAIgB9AH0A</AFEJSONBlob>
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21306,9 +21290,12 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
+    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -21322,12 +21309,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CD460F9D-420A-4723-B323-396E4D19EC9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B6BE249C-20B1-4A62-BBCD-F2A46D88BCAB}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="09eef6d6-daa8-4301-8f9f-b1ec38079286"/>
-    <ds:schemaRef ds:uri="7291119c-fce9-4911-96ae-b800be5dccd8"/>
+    <ds:schemaRef ds:uri="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
+++ b/Excel/Enterprises/Enterprise_Swine_Template_WIP_v01.xlsx
@@ -603,9 +603,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -613,9 +613,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>DD/MM/YYYY or DD Month YYYY</t>
@@ -624,9 +624,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -634,9 +634,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Automatically calculated, 12 months after start date</t>
@@ -660,9 +660,9 @@
   <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">← </t>
@@ -670,9 +670,9 @@
     <r>
       <rPr>
         <i/>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1" tint="0.34998626667073579"/>
-        <rFont val="Times New Roman"/>
+        <rFont val="Arial"/>
         <family val="1"/>
       </rPr>
       <t>Please select</t>
@@ -1260,108 +1260,106 @@
   </numFmts>
   <fonts count="55" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14999847407452621"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF183C1B"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF533001"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
       <i/>
       <strike/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
@@ -1372,219 +1370,217 @@
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="0" tint="-4.9989318521683403E-2"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1" tint="0.14996795556505021"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC44340"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF008000"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="0" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0" tint="-4.9989318521683403E-2"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
       <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1" tint="0.14996795556505021"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC44340"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF008000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <u/>
+      <sz val="9"/>
+      <color theme="1" tint="0.34998626667073579"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="0" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="6" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFCC6600"/>
-      <name val="Times New Roman"/>
+      <i/>
+      <sz val="9"/>
+      <color theme="5" tint="-0.499984740745262"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <u/>
       <sz val="10"/>
-      <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="0.24994659260841701"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="10"/>
-      <color theme="6" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color theme="5" tint="-0.499984740745262"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Times New Roman"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
+      <sz val="9"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1" tint="0.249977111117893"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF242424"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -1592,34 +1588,34 @@
     <font>
       <sz val="9"/>
       <color rgb="FF404040"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.24994659260841701"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="20"/>
+      <sz val="18"/>
       <color rgb="FF0C769E"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
     <font>
       <i/>
-      <sz val="16"/>
+      <sz val="14"/>
       <color theme="1" tint="0.34998626667073579"/>
-      <name val="Times New Roman"/>
+      <name val="Arial"/>
       <family val="1"/>
     </font>
   </fonts>
@@ -2469,11 +2465,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2493,11 +2488,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2517,11 +2511,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2541,11 +2534,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2565,11 +2557,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2589,11 +2580,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2613,11 +2603,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2637,11 +2626,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2661,11 +2649,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2685,11 +2672,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2709,11 +2695,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2733,11 +2718,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2757,11 +2741,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2781,11 +2764,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2805,11 +2787,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2829,11 +2810,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2853,11 +2833,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2877,11 +2856,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2901,11 +2879,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2925,11 +2902,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2949,11 +2925,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2973,11 +2948,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -2997,11 +2971,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3021,11 +2994,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3045,11 +3017,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3069,11 +3040,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3093,11 +3063,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3117,11 +3086,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3141,11 +3109,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3165,11 +3132,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3189,11 +3155,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3213,11 +3178,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3237,11 +3201,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3261,11 +3224,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3285,11 +3247,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3309,11 +3270,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3333,11 +3293,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3357,11 +3316,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3381,11 +3339,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3405,11 +3362,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3429,11 +3385,10 @@
         <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
-        <sz val="11"/>
+        <sz val="10"/>
         <color theme="1"/>
-        <name val="Times New Roman"/>
+        <name val="Arial"/>
         <family val="2"/>
-        <scheme val="minor"/>
       </font>
       <fill>
         <patternFill patternType="none">
@@ -3740,7 +3695,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4231,7 +4186,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -4468,7 +4423,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -4605,7 +4560,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
@@ -6010,24 +5965,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{6496CA75-FED4-4E21-A81D-BDC20736B7B5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6091,24 +6046,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{1A778010-8EF6-4986-9F7A-ED1F5F66D6A5}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6172,24 +6127,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{7DC837A9-60D0-4FEE-9D60-F5F33C8747DB}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6253,24 +6208,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A1C4261C-1106-48B4-9C10-E82D60412011}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6334,24 +6289,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{AE965B10-5BD0-44CC-8118-41596A6F15E2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6415,24 +6370,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{304D704D-8D75-4B25-B661-1CD4BF80A14D}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -6495,16 +6450,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6570,36 +6525,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6665,18 +6620,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -6744,7 +6699,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -6862,16 +6817,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -6937,36 +6892,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -7032,18 +6987,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7211,16 +7166,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7286,36 +7241,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7381,18 +7336,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7454,7 +7409,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -7478,7 +7433,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -7546,7 +7501,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -7669,16 +7624,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7744,36 +7699,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -7839,18 +7794,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8022,7 +7977,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8046,7 +8001,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8108,7 +8063,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8132,7 +8087,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8194,7 +8149,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8218,7 +8173,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8280,7 +8235,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8304,7 +8259,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8366,7 +8321,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8390,7 +8345,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8452,7 +8407,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8476,7 +8431,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8538,7 +8493,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -8562,7 +8517,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -8631,24 +8586,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{325659CC-BF18-4027-9C39-6B59F0E2F578}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8712,24 +8667,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A9E71E38-28CF-40B4-A787-CD2A933BF092}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8793,24 +8748,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{FBAAA7CE-3F73-42A7-B887-E644937F7159}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8874,24 +8829,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{E266E2BA-6A96-4903-9E52-5C6BCFEF9FF1}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -8955,24 +8910,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{F8F36783-2D83-448C-9BE3-D1653ADA37CE}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9036,24 +8991,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9792A2EE-0599-40C6-BEC6-FB928C51F2CA}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9117,24 +9072,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{9FBD39D1-A40C-4D41-815F-1614BABEEB25}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9198,24 +9153,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{48E1D669-5050-474F-B029-B219812AC417}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -9278,16 +9233,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9353,36 +9308,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9448,18 +9403,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9527,7 +9482,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
@@ -9645,16 +9600,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9720,36 +9675,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="0C769E"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="0C769E"/>
             </a:solidFill>
@@ -9815,18 +9770,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -9994,16 +9949,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10069,36 +10024,36 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Including</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t> removals (</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Net emissions)</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10164,18 +10119,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 1</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10237,7 +10192,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10261,7 +10216,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10329,7 +10284,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1600">
+            <a:rPr lang="en-AU" sz="1400">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
@@ -10452,16 +10407,16 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Excluding removals</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="1">
+          <a:endParaRPr lang="en-AU" sz="1000" b="1">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
@@ -10527,18 +10482,18 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="1000" b="0" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:t>Method 2</a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1200" b="0">
+          <a:endParaRPr lang="en-AU" sz="1000" b="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10710,7 +10665,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10779,7 +10734,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10847,7 +10802,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -10871,7 +10826,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -10934,7 +10889,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11003,7 +10958,7 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11071,7 +11026,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11085,7 +11040,7 @@
             <a:t>t CO2-e / tonne manure</a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike" baseline="0">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11099,7 +11054,7 @@
             <a:t> </a:t>
           </a:r>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11123,7 +11078,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11185,7 +11140,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="1100" b="0" i="1" u="none" strike="noStrike">
+            <a:rPr lang="en-AU" sz="1000" b="0" i="1" u="none" strike="noStrike">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="50000"/>
@@ -11209,7 +11164,7 @@
             </a:rPr>
             <a:t> </a:t>
           </a:r>
-          <a:endParaRPr lang="en-AU" sz="1100">
+          <a:endParaRPr lang="en-AU" sz="1000">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="50000"/>
@@ -11278,24 +11233,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{B945A79A-D657-45FF-8794-B3F7FE79A7B2}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11359,24 +11314,24 @@
         <a:p>
           <a:pPr marL="0" indent="0"/>
           <a:fld id="{A0887E06-5564-4610-905A-7D5E4A0E50F4}" type="TxLink">
-            <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike">
+            <a:rPr lang="en-US" sz="2600" b="1" i="0" u="none" strike="noStrike">
               <a:solidFill>
                 <a:srgbClr val="4F4789"/>
               </a:solidFill>
-              <a:latin typeface="Times New Roman"/>
+              <a:latin typeface="Arial"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman"/>
+              <a:cs typeface="Arial"/>
             </a:rPr>
             <a:pPr marL="0" indent="0"/>
             <a:t>#NAME?</a:t>
           </a:fld>
-          <a:endParaRPr lang="en-AU" sz="2800" b="1" i="0" u="none" strike="noStrike">
+          <a:endParaRPr lang="en-AU" sz="2600" b="1" i="0" u="none" strike="noStrike">
             <a:solidFill>
               <a:srgbClr val="4F4789"/>
             </a:solidFill>
-            <a:latin typeface="Times New Roman"/>
+            <a:latin typeface="Arial"/>
             <a:ea typeface="+mn-ea"/>
-            <a:cs typeface="Times New Roman"/>
+            <a:cs typeface="Arial"/>
           </a:endParaRPr>
         </a:p>
       </xdr:txBody>
@@ -11439,7 +11394,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Liveweight sold</a:t>
           </a:r>
         </a:p>
@@ -11576,7 +11531,7 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr lang="en-AU" sz="2000"/>
+            <a:rPr lang="en-AU" sz="1800"/>
             <a:t>Manure sold</a:t>
           </a:r>
         </a:p>
@@ -12457,12 +12412,12 @@
     </a:clrScheme>
     <a:fontScheme name="Custom 1">
       <a:majorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Times New Roman"/>
+        <a:latin typeface="Arial"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -12673,31 +12628,31 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A3" s="80" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="A6" s="81" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
       </c>
     </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -12715,7 +12670,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:K87"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" customWidth="1"/>
@@ -12743,7 +12698,7 @@
       <c r="J1" s="91"/>
       <c r="K1" s="91"/>
     </row>
-    <row r="2" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -12755,7 +12710,7 @@
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
     </row>
-    <row r="3" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -12770,7 +12725,7 @@
       <c r="J3" s="92"/>
       <c r="K3" s="92"/>
     </row>
-    <row r="4" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -12780,10 +12735,10 @@
         <v>Emissions breakdown for activities running between 01 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
     </row>
-    <row r="6" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
@@ -12791,13 +12746,13 @@
         <v>236</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -12822,7 +12777,7 @@
       </c>
       <c r="J8" s="12"/>
     </row>
-    <row r="9" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1" t="s">
         <v>270</v>
@@ -12850,7 +12805,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -12880,7 +12835,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -12911,7 +12866,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -12942,7 +12897,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -12973,7 +12928,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -13004,7 +12959,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>136</v>
@@ -13032,7 +12987,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -13062,7 +13017,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -13093,7 +13048,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -13124,7 +13079,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -13155,7 +13110,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -13186,7 +13141,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="86" t="s">
         <v>5</v>
       </c>
@@ -13205,20 +13160,20 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
       <c r="D24" s="78" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="12" t="s">
         <v>238</v>
       </c>
@@ -13239,7 +13194,7 @@
       </c>
       <c r="J26" s="12"/>
     </row>
-    <row r="27" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="1" t="e" cm="1">
         <f t="array" ref="D27">"14.1.1-2 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13267,7 +13222,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="86" t="s">
         <v>239</v>
       </c>
@@ -13286,15 +13241,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="78" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D33" s="12" t="s">
         <v>241</v>
       </c>
@@ -13315,7 +13270,7 @@
       </c>
       <c r="J33" s="12"/>
     </row>
-    <row r="34" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D34" s="1" t="s">
         <v>276</v>
       </c>
@@ -13342,7 +13297,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="35" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D35" s="1" t="s">
         <v>277</v>
       </c>
@@ -13369,7 +13324,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="36" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D36" s="1" t="s">
         <v>242</v>
       </c>
@@ -13396,7 +13351,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D37" s="1" t="s">
         <v>243</v>
       </c>
@@ -13423,7 +13378,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D38" s="1" t="s">
         <v>278</v>
       </c>
@@ -13450,7 +13405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D39" s="1" t="s">
         <v>244</v>
       </c>
@@ -13477,7 +13432,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D40" s="1" t="s">
         <v>245</v>
       </c>
@@ -13504,7 +13459,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D41" s="1" t="e" cm="1">
         <f t="array" ref="D41">"15.12.1.1 Purchased electricity " &amp; IF(X_Cell_Electricity_CalculationMethod="Location-based (simpler)", "(Location-based)", "(Market-based)")</f>
         <v>#NAME?</v>
@@ -13532,7 +13487,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D42" s="1" t="s">
         <v>247</v>
       </c>
@@ -13559,7 +13514,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D43" s="1" t="s">
         <v>246</v>
       </c>
@@ -13586,7 +13541,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D44" s="1" t="s">
         <v>248</v>
       </c>
@@ -13613,7 +13568,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="86" t="s">
         <v>249</v>
       </c>
@@ -13632,16 +13587,16 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="47" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="48" spans="4:10" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="4:10" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="78" t="str">
         <f>"Carbon removals from plantings for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Carbon removals from plantings for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="49" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="50" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="86" t="s">
         <v>250</v>
       </c>
@@ -13653,16 +13608,16 @@
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="52" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D53" s="78" t="str">
         <f>"Net emissions for the activity period " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Site_EndDate, "d mmmm yyyy")</f>
         <v>Net emissions for the activity period 1 January 2025 and 31 December 2025</v>
       </c>
     </row>
-    <row r="54" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="55" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="12"/>
       <c r="E55" s="12" t="s">
         <v>131</v>
@@ -13672,7 +13627,7 @@
       </c>
       <c r="G55" s="12"/>
     </row>
-    <row r="56" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D56" s="95" t="s">
         <v>251</v>
       </c>
@@ -13688,7 +13643,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="57" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D57" s="95" t="s">
         <v>253</v>
       </c>
@@ -13704,36 +13659,36 @@
         <v>252</v>
       </c>
     </row>
-    <row r="58" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="67" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="70" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="71" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="72" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="73" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="79" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="80" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="81" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="82" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="83" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:7" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="79" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="81" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="82" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13747,7 +13702,7 @@
     <tabColor rgb="FF0C769E"/>
   </sheetPr>
   <dimension ref="A1:P56"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -13757,7 +13712,7 @@
     <col min="14" max="16" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="91" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" s="91" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="A1" s="11" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
@@ -13765,8 +13720,8 @@
         <v>256</v>
       </c>
     </row>
-    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C3" s="92"/>
       <c r="D3" s="92"/>
       <c r="E3" s="92"/>
@@ -13782,13 +13737,13 @@
       <c r="O3" s="92"/>
       <c r="P3" s="92"/>
     </row>
-    <row r="32" spans="4:4" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:4" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D32" s="2" t="str">
         <f>"Emissions for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Emissions for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="12"/>
       <c r="E35" s="12" t="s">
         <v>131</v>
@@ -13798,7 +13753,7 @@
       </c>
       <c r="G35" s="12"/>
     </row>
-    <row r="36" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="76" t="s">
         <v>254</v>
       </c>
@@ -13814,7 +13769,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="76" t="s">
         <v>255</v>
       </c>
@@ -13830,18 +13785,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D39" s="2" t="str">
         <f>"Product emissions intensity for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Product emissions intensity for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="42" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D42" s="78" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="12" t="s">
         <v>133</v>
       </c>
@@ -13864,7 +13819,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="s">
         <v>283</v>
       </c>
@@ -13891,7 +13846,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="45" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="1" t="s">
         <v>284</v>
       </c>
@@ -13918,7 +13873,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>285</v>
       </c>
@@ -13945,7 +13900,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="47" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D47" s="1" t="s">
         <v>286</v>
       </c>
@@ -13972,7 +13927,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="48" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="1" t="s">
         <v>287</v>
       </c>
@@ -13994,12 +13949,12 @@
       </c>
       <c r="J48" s="10"/>
     </row>
-    <row r="50" spans="4:10" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D50" s="78" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="12" t="s">
         <v>133</v>
       </c>
@@ -14022,7 +13977,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="1" t="s">
         <v>283</v>
       </c>
@@ -14049,7 +14004,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="s">
         <v>284</v>
       </c>
@@ -14076,7 +14031,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="s">
         <v>285</v>
       </c>
@@ -14103,7 +14058,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="s">
         <v>286</v>
       </c>
@@ -14130,7 +14085,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="56" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D56" s="1" t="s">
         <v>287</v>
       </c>
@@ -14165,7 +14120,7 @@
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
   <dimension ref="A1:AA115"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="4" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" style="22" customWidth="1"/>
@@ -14186,7 +14141,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:24" s="22" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="22" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -14197,7 +14152,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -14224,7 +14179,7 @@
       <c r="W3" s="24"/>
       <c r="X3" s="24"/>
     </row>
-    <row r="4" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>HYPERLINK("#'Results'!A1", "Results")</f>
         <v>Results</v>
@@ -14239,19 +14194,19 @@
       <c r="J4" s="30"/>
       <c r="K4" s="30"/>
     </row>
-    <row r="5" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="2" t="s">
         <v>96</v>
       </c>
       <c r="N5" s="31"/>
     </row>
-    <row r="6" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>1</v>
       </c>
       <c r="N6" s="33"/>
     </row>
-    <row r="7" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>HYPERLINK("#'Input - Site'!A1", "Site")</f>
         <v>Site</v>
@@ -14263,7 +14218,7 @@
       <c r="F7" s="44"/>
       <c r="G7" s="45"/>
     </row>
-    <row r="8" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Input - Pasture Beef'!A1", "Pasture Beef")</f>
         <v>Pasture Beef</v>
@@ -14275,14 +14230,14 @@
       <c r="F8" s="47"/>
       <c r="G8" s="48"/>
     </row>
-    <row r="9" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="D9" s="1"/>
       <c r="E9" s="49"/>
       <c r="F9" s="17"/>
       <c r="N9" s="35"/>
     </row>
-    <row r="10" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>3</v>
       </c>
@@ -14297,7 +14252,7 @@
       </c>
       <c r="N10" s="35"/>
     </row>
-    <row r="11" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.1-2 Methane'!A1", "4.2.1.1-2 Methane")</f>
         <v>4.2.1.1-2 Methane</v>
@@ -14314,7 +14269,7 @@
       <c r="G11" s="1"/>
       <c r="N11" s="40"/>
     </row>
-    <row r="12" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.3-4 Soil direct N2O'!A1", "4.2.1.3-4 Soil direct N2O")</f>
         <v>4.2.1.3-4 Soil direct N2O</v>
@@ -14329,7 +14284,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.5-6 Soil Atmos Dep'!A1", "4.2.1.5-6 Soil atm. deposition")</f>
         <v>4.2.1.5-6 Soil atm. deposition</v>
@@ -14346,7 +14301,7 @@
       <c r="N13" s="42"/>
       <c r="O13" s="42"/>
     </row>
-    <row r="14" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>HYPERLINK("#'4.2.1.7-8 Soil leach runoff'!A1", "4.2.1.7-8 Soil leach &amp; runoff")</f>
         <v>4.2.1.7-8 Soil leach &amp; runoff</v>
@@ -14363,7 +14318,7 @@
       <c r="N14" s="42"/>
       <c r="O14" s="42"/>
     </row>
-    <row r="15" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="D15" s="1" t="s">
         <v>109</v>
@@ -14377,7 +14332,7 @@
       <c r="N15" s="42"/>
       <c r="O15" s="42"/>
     </row>
-    <row r="16" spans="1:24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>2</v>
       </c>
@@ -14393,7 +14348,7 @@
       <c r="N16" s="42"/>
       <c r="O16" s="42"/>
     </row>
-    <row r="17" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>HYPERLINK("#'Constants - Pasture Beef'!A1", "Constants - Pasture Beef")</f>
         <v>Constants - Pasture Beef</v>
@@ -14408,7 +14363,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>HYPERLINK("#'Constants - Livestock'!A1", "Constants - Livestock")</f>
         <v>Constants - Livestock</v>
@@ -14422,7 +14377,7 @@
       </c>
       <c r="F18" s="17"/>
     </row>
-    <row r="19" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -14437,7 +14392,7 @@
       <c r="G19" s="50"/>
       <c r="N19" s="31"/>
     </row>
-    <row r="20" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -14453,7 +14408,7 @@
       <c r="G20" s="49"/>
       <c r="N20" s="33"/>
     </row>
-    <row r="21" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="1" t="s">
         <v>115</v>
@@ -14465,7 +14420,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="49"/>
     </row>
-    <row r="22" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
       <c r="D22" s="1" t="s">
         <v>69</v>
@@ -14476,29 +14431,29 @@
       </c>
       <c r="G22" s="53"/>
     </row>
-    <row r="23" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="N25" s="33"/>
     </row>
-    <row r="26" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
     </row>
-    <row r="27" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
     </row>
-    <row r="28" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
     </row>
-    <row r="29" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
     </row>
-    <row r="30" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="L30" s="51"/>
       <c r="M30" s="51"/>
@@ -14515,7 +14470,7 @@
       <c r="X30" s="51"/>
       <c r="Y30" s="51"/>
     </row>
-    <row r="31" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
       <c r="L31" s="52"/>
       <c r="M31" s="52"/>
@@ -14532,7 +14487,7 @@
       <c r="X31" s="52"/>
       <c r="Y31" s="52"/>
     </row>
-    <row r="32" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
       <c r="L32" s="52"/>
       <c r="M32" s="52"/>
@@ -14549,7 +14504,7 @@
       <c r="X32" s="52"/>
       <c r="Y32" s="52"/>
     </row>
-    <row r="33" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
       <c r="L33" s="52"/>
       <c r="M33" s="52"/>
@@ -14566,7 +14521,7 @@
       <c r="X33" s="52"/>
       <c r="Y33" s="52"/>
     </row>
-    <row r="34" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="J34" s="54"/>
       <c r="K34" s="55"/>
@@ -14585,7 +14540,7 @@
       <c r="X34" s="52"/>
       <c r="Y34" s="52"/>
     </row>
-    <row r="35" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="J35" s="54"/>
       <c r="K35" s="55"/>
@@ -14604,7 +14559,7 @@
       <c r="X35" s="52"/>
       <c r="Y35" s="52"/>
     </row>
-    <row r="36" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="56"/>
       <c r="E36" s="56"/>
@@ -14629,7 +14584,7 @@
       <c r="X36" s="52"/>
       <c r="Y36" s="52"/>
     </row>
-    <row r="37" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="56"/>
       <c r="E37" s="56"/>
@@ -14654,7 +14609,7 @@
       <c r="X37" s="52"/>
       <c r="Y37" s="52"/>
     </row>
-    <row r="38" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="56"/>
       <c r="E38" s="56"/>
@@ -14679,7 +14634,7 @@
       <c r="X38" s="52"/>
       <c r="Y38" s="52"/>
     </row>
-    <row r="39" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="56"/>
       <c r="E39" s="56"/>
@@ -14704,7 +14659,7 @@
       <c r="X39" s="52"/>
       <c r="Y39" s="52"/>
     </row>
-    <row r="40" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="59"/>
       <c r="E40" s="59"/>
@@ -14729,96 +14684,96 @@
       <c r="X40" s="62"/>
       <c r="Y40" s="62"/>
     </row>
-    <row r="41" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
     </row>
-    <row r="42" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D45" s="2"/>
     </row>
-    <row r="46" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D47" s="63"/>
       <c r="E47" s="63"/>
       <c r="F47" s="63"/>
       <c r="G47" s="63"/>
       <c r="H47" s="63"/>
     </row>
-    <row r="48" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D48" s="64"/>
       <c r="E48" s="64"/>
       <c r="F48" s="65"/>
       <c r="G48" s="65"/>
       <c r="H48" s="64"/>
     </row>
-    <row r="49" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D49" s="64"/>
       <c r="E49" s="64"/>
       <c r="F49" s="65"/>
       <c r="G49" s="65"/>
       <c r="H49" s="64"/>
     </row>
-    <row r="50" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D50" s="64"/>
       <c r="E50" s="64"/>
       <c r="F50" s="65"/>
       <c r="G50" s="65"/>
       <c r="H50" s="64"/>
     </row>
-    <row r="51" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D51" s="66"/>
       <c r="E51" s="67"/>
       <c r="F51" s="67"/>
       <c r="G51" s="67"/>
       <c r="H51" s="68"/>
     </row>
-    <row r="52" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="53" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="54" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G54" s="69"/>
     </row>
-    <row r="55" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D55" s="2"/>
     </row>
-    <row r="56" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="57" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F57" s="70"/>
     </row>
-    <row r="58" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E58" s="71"/>
     </row>
-    <row r="59" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E59" s="71"/>
     </row>
-    <row r="60" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E60" s="72"/>
     </row>
-    <row r="61" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D64" s="1"/>
       <c r="E64" s="71"/>
     </row>
-    <row r="65" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D65" s="1"/>
       <c r="E65" s="71"/>
     </row>
-    <row r="66" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D66" s="1"/>
       <c r="E66" s="72"/>
     </row>
-    <row r="67" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="68" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="69" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D69" s="73"/>
       <c r="E69" s="73"/>
       <c r="F69" s="73"/>
@@ -14826,7 +14781,7 @@
       <c r="H69" s="73"/>
       <c r="I69" s="73"/>
     </row>
-    <row r="70" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D70" s="73"/>
       <c r="E70" s="73"/>
       <c r="F70" s="73"/>
@@ -14834,7 +14789,7 @@
       <c r="H70" s="73"/>
       <c r="I70" s="73"/>
     </row>
-    <row r="71" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D71" s="73"/>
       <c r="E71" s="73"/>
       <c r="F71" s="73"/>
@@ -14842,7 +14797,7 @@
       <c r="H71" s="73"/>
       <c r="I71" s="73"/>
     </row>
-    <row r="72" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D72" s="73"/>
       <c r="E72" s="73"/>
       <c r="F72" s="73"/>
@@ -14850,59 +14805,59 @@
       <c r="H72" s="73"/>
       <c r="I72" s="73"/>
     </row>
-    <row r="73" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="74" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="77" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="78" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="74" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="75" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="76" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="77" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="78" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D78" s="74"/>
     </row>
-    <row r="79" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D79" s="74"/>
     </row>
-    <row r="80" spans="4:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:9" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D80" s="74"/>
     </row>
-    <row r="81" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D81" s="74"/>
     </row>
-    <row r="82" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D82" s="74"/>
     </row>
-    <row r="83" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="84" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="85" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="86" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="87" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="89" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="90" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="91" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="92" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="93" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="94" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="95" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="96" spans="4:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="97" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="98" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="99" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="100" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="101" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="102" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="103" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="104" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="105" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="106" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="107" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="108" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="109" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="110" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="111" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="112" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="114" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="115" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="83" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="84" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="85" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="86" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="87" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="89" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="90" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="91" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="92" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" spans="4:4" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="98" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="99" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="100" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="101" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="102" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="103" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="104" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="105" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="106" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="107" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="108" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="109" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="110" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="111" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="112" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="115" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E12" xr:uid="{620909BD-05B7-4260-BB85-4888DFAEE1F3}">
@@ -14928,7 +14883,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:J78"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -14939,7 +14894,7 @@
     <col min="11" max="11" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:10" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:10" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="28" t="s">
         <v>140</v>
       </c>
@@ -14951,7 +14906,7 @@
       <c r="I1" s="22"/>
       <c r="J1" s="22"/>
     </row>
-    <row r="2" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
@@ -14961,7 +14916,7 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
     </row>
-    <row r="3" spans="3:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -14971,7 +14926,7 @@
       <c r="I3" s="29"/>
       <c r="J3" s="29"/>
     </row>
-    <row r="5" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>88</v>
       </c>
@@ -14979,13 +14934,13 @@
       <c r="F5" s="25"/>
       <c r="G5" s="25"/>
     </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D6" s="32"/>
       <c r="E6" s="25"/>
       <c r="F6" s="25"/>
       <c r="G6" s="25"/>
     </row>
-    <row r="7" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="1" t="s">
         <v>89</v>
       </c>
@@ -14995,7 +14950,7 @@
       <c r="F7" s="17"/>
       <c r="G7" s="25"/>
     </row>
-    <row r="8" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="13" t="s">
         <v>91</v>
       </c>
@@ -15005,13 +14960,13 @@
       <c r="F8" s="25"/>
       <c r="G8" s="25"/>
     </row>
-    <row r="9" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
       <c r="F9" s="25"/>
       <c r="G9" s="25"/>
     </row>
-    <row r="10" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="36" t="s">
         <v>93</v>
       </c>
@@ -15019,13 +14974,13 @@
       <c r="F10" s="38"/>
       <c r="G10" s="39"/>
     </row>
-    <row r="11" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
       <c r="F11" s="25"/>
       <c r="G11" s="25"/>
     </row>
-    <row r="12" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="13" t="s">
         <v>17</v>
       </c>
@@ -15037,7 +14992,7 @@
       </c>
       <c r="G12" s="25"/>
     </row>
-    <row r="13" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D13" s="13" t="s">
         <v>18</v>
       </c>
@@ -15050,16 +15005,16 @@
       </c>
       <c r="G13" s="25"/>
     </row>
-    <row r="14" spans="3:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
     </row>
-    <row r="16" spans="3:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D16" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="s">
         <v>14</v>
       </c>
@@ -15070,7 +15025,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="s">
         <v>15</v>
       </c>
@@ -15081,7 +15036,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="20" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="s">
         <v>16</v>
       </c>
@@ -15093,7 +15048,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="22" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="s">
         <v>267</v>
       </c>
@@ -15105,7 +15060,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="s">
         <v>268</v>
       </c>
@@ -15116,7 +15071,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D24" s="1" t="s">
         <v>281</v>
       </c>
@@ -15127,7 +15082,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D25" s="1" t="s">
         <v>282</v>
       </c>
@@ -15138,7 +15093,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="27" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D27" s="1" t="s">
         <v>279</v>
       </c>
@@ -15149,7 +15104,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="28" spans="4:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:6" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="1" t="s">
         <v>280</v>
       </c>
@@ -15160,18 +15115,18 @@
         <v>141</v>
       </c>
     </row>
-    <row r="31" spans="4:6" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:6" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D31" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="34" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D34" s="78" t="str">
         <f>"Carbon captured from " &amp; TEXT(X_Cell_Site_StartDate, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Site_EndDate, "d, mmmm, yyyy") &amp; " from environmental plantings"</f>
         <v>Carbon captured from 1 January 2025 to 31, December, 2025 from environmental plantings</v>
       </c>
     </row>
-    <row r="36" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D36" s="20" t="s">
         <v>230</v>
       </c>
@@ -15185,7 +15140,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="37" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D37" s="34"/>
       <c r="E37" s="75"/>
       <c r="F37" s="19"/>
@@ -15194,29 +15149,29 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="4:7" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D41" s="2" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="43" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D43" s="78" t="str">
         <f>"Gross emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Gross emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="45" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D45" s="88" t="str" cm="1">
         <f t="array" ref="D45">"There are " &amp; Common_InputFunctions.getOverlappingReportingCycles(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate) &amp; " emissions calculation periods that need to be completed before total product emissions can be determined."</f>
         <v>There are 2 emissions calculation periods that need to be completed before total product emissions can be determined.</v>
       </c>
     </row>
-    <row r="46" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D46" s="1" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="48" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D48" s="79" t="s">
         <v>116</v>
       </c>
@@ -15227,7 +15182,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="49" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D49" s="1" t="str" cm="1">
         <f t="array" ref="D49:D50">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15244,7 +15199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="50" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15260,7 +15215,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="51" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E51" s="75">
         <f>IF(ISBLANK($D51), 0, IF(ISNUMBER(SEARCH("reporting", $D51)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15273,7 +15228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="52" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E52" s="75">
         <f>IF(ISBLANK($D52), 0, IF(ISNUMBER(SEARCH("reporting", $D52)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15286,7 +15241,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="53" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E53" s="75">
         <f>IF(ISBLANK($D53), 0, IF(ISNUMBER(SEARCH("reporting", $D53)), Result_Enterprise_Gross_Method1, "Enter value"))</f>
         <v>0</v>
@@ -15299,7 +15254,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="54" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="89" t="s">
         <v>129</v>
       </c>
@@ -15315,13 +15270,13 @@
         <v>8</v>
       </c>
     </row>
-    <row r="59" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D59" s="78" t="str">
         <f>"Carbon removals from environmental plantings for whole production cycle running between " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " and " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Carbon removals from environmental plantings for whole production cycle running between 1 November 2025 and 31 March 2026</v>
       </c>
     </row>
-    <row r="61" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D61" s="79" t="s">
         <v>116</v>
       </c>
@@ -15330,7 +15285,7 @@
       </c>
       <c r="F61" s="79"/>
     </row>
-    <row r="62" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D62" s="1" t="str" cm="1">
         <f t="array" ref="D62:D63">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15343,7 +15298,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="63" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D63" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15355,7 +15310,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="64" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E64" s="75">
         <f>IF(ISBLANK($D64), 0, IF(ISNUMBER(SEARCH("reporting", $D64)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15364,7 +15319,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E65" s="75">
         <f>IF(ISBLANK($D65), 0, IF(ISNUMBER(SEARCH("reporting", $D65)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15373,7 +15328,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="66" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E66" s="75">
         <f>IF(ISBLANK($D66), 0, IF(ISNUMBER(SEARCH("reporting", $D66)), SUM(Table_Input_Enterprise_PlantingRemovals[Removal allocated to this enterprise]), "Enter value"))</f>
         <v>0</v>
@@ -15382,7 +15337,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="67" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D67" s="89" t="s">
         <v>130</v>
       </c>
@@ -15394,13 +15349,13 @@
         <v>128</v>
       </c>
     </row>
-    <row r="70" spans="4:7" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:7" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D70" s="78" t="str">
         <f>"Net emissions from other activity periods in the production timeframe " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeStart, "d mmmm yyyy") &amp; " to " &amp; TEXT(X_Cell_Enterprise_ProductionTimeframeEnd, "d mmmm yyyy")</f>
         <v>Net emissions from other activity periods in the production timeframe 1 November 2025 to 31 March 2026</v>
       </c>
     </row>
-    <row r="72" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D72" s="79" t="s">
         <v>116</v>
       </c>
@@ -15411,7 +15366,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="73" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D73" s="1" t="str" cm="1">
         <f t="array" ref="D73:D74">Common_InputFunctions.getOverlappingReportingPeriods(X_Cell_Enterprise_ProductionTimeframeStart,X_Cell_Enterprise_ProductionTimeframeEnd,X_Cell_Site_StartDate)</f>
         <v>01 Jan 2025 to 31 Dec 2025 (This reporting cycle)</v>
@@ -15428,7 +15383,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D74" s="1" t="str">
         <v>01 Jan 2026 to 31 Dec 2026</v>
       </c>
@@ -15444,7 +15399,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="75" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E75" s="75">
         <f>IF(ISBLANK($D75), 0, IF(ISNUMBER(SEARCH("reporting", $D75)), E51-$E$64, "Enter value"))</f>
         <v>0</v>
@@ -15457,7 +15412,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="76" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E76" s="75">
         <f>IF(ISBLANK($D76), 0, IF(ISNUMBER(SEARCH("reporting", $D76)), E52-$E$65, "Enter value"))</f>
         <v>0</v>
@@ -15470,7 +15425,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="77" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="E77" s="75">
         <f>IF(ISBLANK($D77), 0, IF(ISNUMBER(SEARCH("reporting", $D77)), E53-$E$66, "Enter value"))</f>
         <v>0</v>
@@ -15483,7 +15438,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="78" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:7" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D78" s="89" t="s">
         <v>129</v>
       </c>
@@ -15513,7 +15468,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M45"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15527,8 +15482,8 @@
         <v>258</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -15541,13 +15496,13 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="4" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="5" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="5" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D5" s="88" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="6" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D6" s="20" t="s">
         <v>260</v>
       </c>
@@ -15567,7 +15522,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D7" s="34"/>
       <c r="E7" s="14" t="s">
         <v>266</v>
@@ -15586,7 +15541,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="8" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D8" s="34"/>
       <c r="E8" s="14"/>
       <c r="F8" s="98"/>
@@ -15597,7 +15552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="34"/>
       <c r="E9" s="14"/>
       <c r="F9" s="98"/>
@@ -15608,7 +15563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="34"/>
       <c r="E10" s="14"/>
       <c r="F10" s="98"/>
@@ -15619,7 +15574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="34"/>
       <c r="E11" s="14"/>
       <c r="F11" s="98"/>
@@ -15630,7 +15585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="34"/>
       <c r="E12" s="14"/>
       <c r="F12" s="98"/>
@@ -15641,7 +15596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="34"/>
       <c r="E13" s="14"/>
       <c r="F13" s="98"/>
@@ -15652,7 +15607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="34"/>
       <c r="E14" s="14"/>
       <c r="F14" s="98"/>
@@ -15663,7 +15618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="34"/>
       <c r="E15" s="14"/>
       <c r="F15" s="98"/>
@@ -15674,7 +15629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="3:13" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="34"/>
       <c r="E16" s="14"/>
       <c r="F16" s="98"/>
@@ -15685,35 +15640,35 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="37" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="38" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="39" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="40" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="41" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="43" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="44" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="20" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E7:E16" xr:uid="{083DF14A-00E2-452A-8599-A053B3BDEC80}">
@@ -15733,7 +15688,7 @@
     <tabColor rgb="FFCC6600"/>
   </sheetPr>
   <dimension ref="C1:M58"/>
-  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
     <col min="2" max="2" width="4.7109375" customWidth="1"/>
@@ -15746,13 +15701,13 @@
     <col min="14" max="14" width="30.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:13" s="11" customFormat="1" ht="25.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="3:13" s="11" customFormat="1" ht="30" x14ac:dyDescent="0.35" customHeight="1">
       <c r="C1" s="11" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="3:13" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:13" s="3" customFormat="1" x14ac:dyDescent="0.25" ht="20" customHeight="1"/>
+    <row r="3" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="C3" s="29"/>
       <c r="D3" s="29"/>
       <c r="E3" s="29"/>
@@ -15765,12 +15720,12 @@
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
     </row>
-    <row r="5" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D5" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="7" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D7" s="79" t="s">
         <v>221</v>
       </c>
@@ -15793,7 +15748,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="8" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D8" s="1" t="str">
         <f>"Liveweight sold"</f>
         <v>Liveweight sold</v>
@@ -15814,7 +15769,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D9" s="1" t="str">
         <f>"Manure produced"</f>
         <v>Manure produced</v>
@@ -15835,7 +15790,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D10" s="1" t="str">
         <f>"Manure sold"</f>
         <v>Manure sold</v>
@@ -15856,7 +15811,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D11" s="1" t="str">
         <f>"Percent income from liveweight sold"</f>
         <v>Percent income from liveweight sold</v>
@@ -15877,7 +15832,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D12" s="1" t="str">
         <f>"Percent income from manure sold"</f>
         <v>Percent income from manure sold</v>
@@ -15898,18 +15853,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="3:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="3:13" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J14" s="84">
         <f>SUM(Table_Input_DataQuality_Enterprise[Score])</f>
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="3:13" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="3:13" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D15" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="17" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D17" s="79" t="s">
         <v>221</v>
       </c>
@@ -15932,7 +15887,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D18" s="1" t="str">
         <f>"Leaching zone"</f>
         <v>Leaching zone</v>
@@ -15953,7 +15908,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="19" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D19" s="1" t="str">
         <f>"Elevation"</f>
         <v>Elevation</v>
@@ -15974,7 +15929,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="20" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D20" s="1" t="str">
         <f>"Average temperature for reporting period"</f>
         <v>Average temperature for reporting period</v>
@@ -15995,7 +15950,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D21" s="1" t="str">
         <f>"Total rainfall for reporting period"</f>
         <v>Total rainfall for reporting period</v>
@@ -16016,7 +15971,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D22" s="1" t="str">
         <f>"Potential evapotranspiration for reporting period"</f>
         <v>Potential evapotranspiration for reporting period</v>
@@ -16037,7 +15992,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D23" s="1" t="str">
         <f>"Number of frost days for reporting period"</f>
         <v>Number of frost days for reporting period</v>
@@ -16058,18 +16013,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J25" s="84">
         <f>SUM(Table_Input_DataQuality_Site[Score])</f>
         <v>73</v>
       </c>
     </row>
-    <row r="26" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D26" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="28" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D28" s="79" t="s">
         <v>221</v>
       </c>
@@ -16092,7 +16047,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="29" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D29" s="1" t="str">
         <f>"Head count"</f>
         <v>Head count</v>
@@ -16113,7 +16068,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D30" s="1" t="str">
         <f>"Duration of stay"</f>
         <v>Duration of stay</v>
@@ -16128,7 +16083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D31" s="1" t="str">
         <f>"Volatile solid production"</f>
         <v>Volatile solid production</v>
@@ -16149,7 +16104,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D32" s="1" t="str">
         <f>"Nitrogen in waste"</f>
         <v>Nitrogen in waste</v>
@@ -16170,7 +16125,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="33" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D33" s="1" t="str">
         <f>"Production and manure management systems"</f>
         <v>Production and manure management systems</v>
@@ -16191,7 +16146,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D34" s="1" t="str">
         <f>"Livestock sales"</f>
         <v>Livestock sales</v>
@@ -16206,7 +16161,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D35" s="1" t="str">
         <f>"Livestock purchases"</f>
         <v>Livestock purchases</v>
@@ -16221,18 +16176,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J37" s="84">
         <f>SUM(Table_Input_DataQuality_PastureManagement[Score])</f>
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D38" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="40" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D40" s="79" t="s">
         <v>221</v>
       </c>
@@ -16255,7 +16210,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="41" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D41" s="1" t="str">
         <f>"Fuel purchases"</f>
         <v>Fuel purchases</v>
@@ -16276,7 +16231,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D42" s="1" t="str">
         <f>"Fuel consumption"</f>
         <v>Fuel consumption</v>
@@ -16297,7 +16252,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D43" s="1" t="str">
         <f>"Electricity consumption"</f>
         <v>Electricity consumption</v>
@@ -16318,7 +16273,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D44" s="1" t="str">
         <f>"Electricity generation"</f>
         <v>Electricity generation</v>
@@ -16339,18 +16294,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="46" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J46" s="84">
         <f>SUM(Table_Input_DataQuality_FuelElectricity[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="4:10" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D48" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="50" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D50" s="79" t="s">
         <v>221</v>
       </c>
@@ -16373,7 +16328,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="51" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D51" s="1" t="str">
         <f>"Farm input purchases"</f>
         <v>Farm input purchases</v>
@@ -16394,7 +16349,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="52" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D52" s="1" t="str">
         <f>"Inbound freight use"</f>
         <v>Inbound freight use</v>
@@ -16415,7 +16370,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="53" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D53" s="1" t="str">
         <f>"Outbound freight use"</f>
         <v>Outbound freight use</v>
@@ -16436,7 +16391,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="54" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D54" s="1" t="str">
         <f>"Use of contractors and service providers"</f>
         <v>Use of contractors and service providers</v>
@@ -16451,7 +16406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D55" s="1" t="str">
         <f>"Solid waste generation and treatment"</f>
         <v>Solid waste generation and treatment</v>
@@ -16472,13 +16427,13 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="4:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:10" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="J57" s="84">
         <f>SUM(Table_Input_DataQuality_FarmInputsFreightWaste[Score])</f>
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="4:10" ht="20.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:10" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D58" s="86" t="s">
         <v>228</v>
       </c>
@@ -16516,7 +16471,7 @@
     <tabColor theme="2" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1:BY297"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="20" x14ac:dyDescent="0.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="22" customWidth="1"/>
     <col min="2" max="2" width="2.7109375" style="22" customWidth="1"/>
@@ -16549,10 +16504,10 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:65" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:65" s="3" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2"/>
     </row>
-    <row r="3" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>HYPERLINK("#'Home'!A1", "Home")</f>
         <v>Home</v>
@@ -16579,11 +16534,11 @@
       <c r="V3" s="24"/>
       <c r="W3" s="24"/>
     </row>
-    <row r="4" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4"/>
       <c r="BM4" s="25"/>
     </row>
-    <row r="5" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="D5" s="2" t="str" cm="1">
         <f t="array" ref="D5">Common_SourceData.Common_SourceData_AustralianStatesTerritories_Title()</f>
@@ -16591,7 +16546,7 @@
       </c>
       <c r="BM5" s="25"/>
     </row>
-    <row r="6" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="81" t="s">
         <v>2</v>
       </c>
@@ -16605,7 +16560,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="82" t="str">
         <f>HYPERLINK("#'Constants - Common'!A1", "Constants - Common")</f>
         <v>Constants - Common</v>
@@ -16623,7 +16578,7 @@
         <v>NSW</v>
       </c>
     </row>
-    <row r="8" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>HYPERLINK("#'Acknowledgements'!A1", "Acknowledgements")</f>
         <v>Acknowledgements</v>
@@ -16641,7 +16596,7 @@
         <v>ACT</v>
       </c>
     </row>
-    <row r="9" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9"/>
       <c r="D9" s="20" t="str" cm="1">
         <f t="array" ref="D9">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16656,7 +16611,7 @@
         <v>VIC</v>
       </c>
     </row>
-    <row r="10" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10"/>
       <c r="D10" s="20" t="str" cm="1">
         <f t="array" ref="D10">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16671,7 +16626,7 @@
         <v>QLD</v>
       </c>
     </row>
-    <row r="11" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11"/>
       <c r="D11" s="20" t="str" cm="1">
         <f t="array" ref="D11">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16687,7 +16642,7 @@
       </c>
       <c r="BM11" s="25"/>
     </row>
-    <row r="12" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12"/>
       <c r="D12" s="20" t="str" cm="1">
         <f t="array" ref="D12">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16703,7 +16658,7 @@
       </c>
       <c r="BM12" s="25"/>
     </row>
-    <row r="13" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13"/>
       <c r="D13" s="20" t="str" cm="1">
         <f t="array" ref="D13">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16718,7 +16673,7 @@
         <v>TAS</v>
       </c>
     </row>
-    <row r="14" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14"/>
       <c r="D14" s="20" t="str" cm="1">
         <f t="array" ref="D14">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_AustralianStatesTerritories_Data(),Table_AustralianStates[[#Headers],[State/Territory]],0)</f>
@@ -16733,129 +16688,129 @@
         <v>NT</v>
       </c>
     </row>
-    <row r="15" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:65" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:65" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16"/>
     </row>
-    <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17"/>
     </row>
-    <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18"/>
       <c r="D18" s="2" t="str" cm="1">
         <f t="array" ref="D18">Common_SourceData.Common_SourceData_WASA4Areas_Title()</f>
         <v>ABS Statistcal Areas Level 4 - Western Australia</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19"/>
       <c r="D19" s="18" t="str" cm="1">
         <f t="array" ref="D19">Common_SourceData.Common_SourceData_WASA4Areas_Source()</f>
         <v>Australian Bureau of Statistics (ABS) - Statistical Areas Level 2 - 2021 - Shapefile</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20"/>
       <c r="D20" s="20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21"/>
       <c r="D21" s="20" t="str" cm="1">
         <f t="array" ref="D21">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Bunbury</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22"/>
       <c r="D22" s="20" t="str" cm="1">
         <f t="array" ref="D22">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Mandurah</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23"/>
       <c r="D23" s="20" t="str" cm="1">
         <f t="array" ref="D23">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - Inner</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24"/>
       <c r="D24" s="20" t="str" cm="1">
         <f t="array" ref="D24">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North East</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25"/>
       <c r="D25" s="20" t="str" cm="1">
         <f t="array" ref="D25">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - North West</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26"/>
       <c r="D26" s="20" t="str" cm="1">
         <f t="array" ref="D26">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South East</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27"/>
       <c r="D27" s="20" t="str" cm="1">
         <f t="array" ref="D27">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Perth - South West</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28"/>
       <c r="D28" s="20" t="str" cm="1">
         <f t="array" ref="D28">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Wheat Belt</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29"/>
       <c r="D29" s="20" t="str" cm="1">
         <f t="array" ref="D29">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (North)</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30"/>
       <c r="D30" s="20" t="str" cm="1">
         <f t="array" ref="D30">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WASA4Areas_Data(), Table_WASA4Areas[[#Headers],[SA 4 Name]], 0)</f>
         <v>Western Australia - Outback (South)</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31"/>
     </row>
-    <row r="32" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32"/>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33"/>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34"/>
       <c r="D34" s="2" t="str" cm="1">
         <f t="array" ref="D34">Common_SourceData.Common_SourceData_GWP_Title()</f>
         <v>Global warming potential for greenhouse gases</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35"/>
       <c r="D35" s="18" t="str" cm="1">
         <f t="array" ref="D35">Common_SourceData.Common_SourceData_GWP_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36"/>
       <c r="D36" s="20" t="s">
         <v>26</v>
@@ -16864,7 +16819,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37"/>
       <c r="D37" s="20" t="str" cm="1">
         <f t="array" ref="D37">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16875,7 +16830,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38"/>
       <c r="D38" s="20" t="str" cm="1">
         <f t="array" ref="D38">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16886,7 +16841,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39"/>
       <c r="D39" s="20" t="str" cm="1">
         <f t="array" ref="D39">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16897,7 +16852,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40"/>
       <c r="D40" s="20" t="str" cm="1">
         <f t="array" ref="D40">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16908,7 +16863,7 @@
         <v>6630</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41"/>
       <c r="D41" s="20" t="str" cm="1">
         <f t="array" ref="D41">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16919,7 +16874,7 @@
         <v>12200</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42"/>
       <c r="D42" s="20" t="str" cm="1">
         <f t="array" ref="D42">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16930,7 +16885,7 @@
         <v>22800</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43"/>
       <c r="D43" s="20" t="str" cm="1">
         <f t="array" ref="D43">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_GWP_Data(), Table_GWPData[[#Headers],[Gas]], 0)</f>
@@ -16941,24 +16896,24 @@
         <v>17200</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45"/>
       <c r="D45" s="2" t="str" cm="1">
         <f t="array" ref="D45">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Title()</f>
         <v>Factor to convert elemental mass of gas to molecular mass</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46"/>
       <c r="D46" s="18" t="str" cm="1">
         <f t="array" ref="D46">Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Source()</f>
         <v>XXXXXXX</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47"/>
       <c r="D47" s="20" t="s">
         <v>26</v>
@@ -16976,7 +16931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48"/>
       <c r="D48" s="20" t="str" cm="1">
         <f t="array" ref="D48">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -16999,7 +16954,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49"/>
       <c r="D49" s="20" t="str" cm="1">
         <f t="array" ref="D49">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17022,7 +16977,7 @@
         <v>1.3333333333333333</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50"/>
       <c r="D50" s="20" t="str" cm="1">
         <f t="array" ref="D50">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17045,7 +17000,7 @@
         <v>1.5714285714285714</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51"/>
       <c r="D51" s="20" t="str" cm="1">
         <f t="array" ref="D51">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17068,7 +17023,7 @@
         <v>3.2857142857142856</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="D52" s="20" t="str" cm="1">
         <f t="array" ref="D52">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17091,7 +17046,7 @@
         <v>2.3333333333333335</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53"/>
       <c r="D53" s="20" t="str" cm="1">
         <f t="array" ref="D53">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17114,7 +17069,7 @@
         <v>3.6666666666666665</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54"/>
       <c r="D54" s="20" t="str" cm="1">
         <f t="array" ref="D54">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ConvertGasElementalToMolecular_Data(),Table_GasToMolecularConversionFactor[[#Headers],[Gas]], 0)</f>
@@ -17137,49 +17092,49 @@
         <v>1.1666666666666667</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="D57" s="2" t="str" cm="1">
         <f t="array" ref="D57">Common_SourceData.Common_SourceData_WetAndDryZones_Title()</f>
         <v>VEERG Australian wet and dry zones</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="D58" s="18" t="str" cm="1">
         <f t="array" ref="D58">Common_SourceData.Common_SourceData_WetAndDryZones_Source()</f>
         <v>VEERG 2026: Table 1.2: Translating climate zones to wet and dry zones</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="D59" s="26" t="str" cm="1">
         <f t="array" ref="D59:D61">"⚠️" &amp; Common_SourceData.Common_SourceData_WetAndDryZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="D60" s="26" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="61" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="D61" s="26" t="str">
         <v>⚠️Fixed typo - Changed 'Fry' to 'Dry'.</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="D63" s="20" t="s">
         <v>32</v>
@@ -17188,7 +17143,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="D64" s="20" t="str" cm="1">
         <f t="array" ref="D64">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17199,7 +17154,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="D65" s="20" t="str" cm="1">
         <f t="array" ref="D65">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17210,7 +17165,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="66" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66"/>
       <c r="D66" s="20" t="str" cm="1">
         <f t="array" ref="D66">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17221,7 +17176,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67"/>
       <c r="D67" s="20" t="str" cm="1">
         <f t="array" ref="D67">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17232,7 +17187,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="68" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68"/>
       <c r="D68" s="20" t="str" cm="1">
         <f t="array" ref="D68">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17243,7 +17198,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69"/>
       <c r="D69" s="20" t="str" cm="1">
         <f t="array" ref="D69">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17254,7 +17209,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70"/>
       <c r="D70" s="20" t="str" cm="1">
         <f t="array" ref="D70">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17265,7 +17220,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71"/>
       <c r="D71" s="20" t="str" cm="1">
         <f t="array" ref="D71">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17276,7 +17231,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72"/>
       <c r="D72" s="20" t="str" cm="1">
         <f t="array" ref="D72">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17287,7 +17242,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73"/>
       <c r="D73" s="20" t="str" cm="1">
         <f t="array" ref="D73">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17298,7 +17253,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
       <c r="D74" s="20" t="str" cm="1">
         <f t="array" ref="D74">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17309,7 +17264,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75"/>
       <c r="D75" s="20" t="str" cm="1">
         <f t="array" ref="D75">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17320,7 +17275,7 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76"/>
       <c r="D76" s="20" t="str" cm="1">
         <f t="array" ref="D76">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17331,7 +17286,7 @@
         <v>Wet climate zone</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77"/>
       <c r="D77" s="20" t="str" cm="1">
         <f t="array" ref="D77">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_WetAndDryZones_Data(), Table_SourceData_WetDryZones[[#Headers],[Climate zone]], 0)</f>
@@ -17342,64 +17297,64 @@
         <v>Dry climate zone</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78"/>
     </row>
-    <row r="79" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79"/>
     </row>
-    <row r="80" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80"/>
     </row>
-    <row r="81" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81"/>
       <c r="D81" s="2" t="str" cm="1">
         <f t="array" ref="D81">Common_SourceData.Common_SourceData_ClimateZones_Title()</f>
         <v>VEERG Australian climate zones</v>
       </c>
     </row>
-    <row r="82" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82"/>
       <c r="D82" s="18" t="str" cm="1">
         <f t="array" ref="D82">Common_SourceData.Common_SourceData_ClimateZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="83" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83"/>
       <c r="D83" s="26" t="str" cm="1">
         <f t="array" ref="D83:D87">"⚠️" &amp; Common_SourceData.Common_SourceData_ClimateZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="84" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="D84" s="26" t="str">
         <v>⚠️Added warm / cool temperate moist / dry - low frost and high temp classes to accommodate climate scenarios excluded by VEERG criteria.</v>
       </c>
     </row>
-    <row r="85" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="D85" s="26" t="str">
         <v>⚠️Fixed typo in MAT value for warm temperate dry - changed 10 to 11.</v>
       </c>
     </row>
-    <row r="86" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="D86" s="26" t="str">
         <v>⚠️Added min and max columns for MAT, MAP, frost days per year, elevation, MAP:PET to calculate zones from real climate data.</v>
       </c>
     </row>
-    <row r="87" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="D87" s="26" t="str">
         <v>⚠️GAF accepts rainfall as a proxy for precipitation.</v>
       </c>
     </row>
-    <row r="88" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="D89" s="20" t="s">
         <v>32</v>
@@ -17451,7 +17406,7 @@
       </c>
       <c r="T89" s="20"/>
     </row>
-    <row r="90" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="D90" s="20" t="str" cm="1">
         <f t="array" ref="D90">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17519,7 +17474,7 @@
       </c>
       <c r="T90" s="20"/>
     </row>
-    <row r="91" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="D91" s="20" t="str" cm="1">
         <f t="array" ref="D91">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17587,7 +17542,7 @@
       </c>
       <c r="T91" s="20"/>
     </row>
-    <row r="92" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="D92" s="20" t="str" cm="1">
         <f t="array" ref="D92">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17655,7 +17610,7 @@
       </c>
       <c r="T92" s="20"/>
     </row>
-    <row r="93" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="D93" s="20" t="str" cm="1">
         <f t="array" ref="D93">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17723,7 +17678,7 @@
       </c>
       <c r="T93" s="20"/>
     </row>
-    <row r="94" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="D94" s="20" t="str" cm="1">
         <f t="array" ref="D94">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17791,7 +17746,7 @@
       </c>
       <c r="T94" s="20"/>
     </row>
-    <row r="95" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="D95" s="20" t="str" cm="1">
         <f t="array" ref="D95">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17859,7 +17814,7 @@
       </c>
       <c r="T95" s="20"/>
     </row>
-    <row r="96" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="D96" s="20" t="str" cm="1">
         <f t="array" ref="D96">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17927,7 +17882,7 @@
       </c>
       <c r="T96" s="20"/>
     </row>
-    <row r="97" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97"/>
       <c r="D97" s="20" t="str" cm="1">
         <f t="array" ref="D97">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_ClimateZones_Data(), Table_SourceData_ClimateZones[[#Headers],[Climate zone]], 0)</f>
@@ -17995,66 +17950,66 @@
       </c>
       <c r="T97" s="20"/>
     </row>
-    <row r="98" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98"/>
     </row>
-    <row r="99" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99"/>
       <c r="D99" s="10" t="str" cm="1">
         <f t="array" ref="D99:D102">Common_SourceData.Common_SourceData_ClimateZones_Appendices()</f>
         <v>Note:</v>
       </c>
     </row>
-    <row r="100" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100"/>
       <c r="D100" s="10" t="str">
         <v>MAT = mean annual temperature</v>
       </c>
     </row>
-    <row r="101" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101"/>
       <c r="D101" s="10" t="str">
         <v>MAP = mean annual precipitation</v>
       </c>
     </row>
-    <row r="102" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102"/>
       <c r="D102" s="10" t="str">
         <v>PET = potential evapotranspiration</v>
       </c>
     </row>
-    <row r="103" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103"/>
       <c r="D103" s="10"/>
     </row>
-    <row r="104" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105"/>
       <c r="D105" s="2" t="str" cm="1">
         <f t="array" ref="D105">Common_SourceData.Common_SourceData_TemperatureZones_Title()</f>
         <v>VEERG Australian temperature zones</v>
       </c>
     </row>
-    <row r="106" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106"/>
       <c r="D106" s="18" t="str" cm="1">
         <f t="array" ref="D106">Common_SourceData.Common_SourceData_TemperatureZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="107" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107"/>
       <c r="D107" s="26" t="str" cm="1">
         <f t="array" ref="D107">"⚠️" &amp; Common_SourceData.Common_SourceData_TemperatureZones_Variation()</f>
         <v>⚠️VARIATION OF SOURCE DATA: Added extra MAT min and MAT max columns to calculate zone from real temperature data.</v>
       </c>
     </row>
-    <row r="108" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109"/>
       <c r="D109" s="20" t="s">
         <v>49</v>
@@ -18069,7 +18024,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="110" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110"/>
       <c r="D110" s="20" t="str" cm="1">
         <f t="array" ref="D110">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18088,7 +18043,7 @@
         <v>999999</v>
       </c>
     </row>
-    <row r="111" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="D111" s="20" t="str" cm="1">
         <f t="array" ref="D111">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18107,7 +18062,7 @@
         <v>25.998999999999999</v>
       </c>
     </row>
-    <row r="112" spans="1:20" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:20" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="D112" s="20" t="str" cm="1">
         <f t="array" ref="D112">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_TemperatureZones_Data(),Table_SourceData_TemperatureZones[[#Headers],[Temperature Zone]],0)</f>
@@ -18126,13 +18081,13 @@
         <v>14.999000000000001</v>
       </c>
     </row>
-    <row r="113" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113"/>
     </row>
-    <row r="114" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114"/>
     </row>
-    <row r="115" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115"/>
       <c r="D115" s="2" t="str" cm="1">
         <f t="array" ref="D115">Common_SourceData.Common_SourceData_RainfallZones_Title()</f>
@@ -18140,7 +18095,7 @@
       </c>
       <c r="BN115" s="22"/>
     </row>
-    <row r="116" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116"/>
       <c r="D116" s="18" t="str" cm="1">
         <f t="array" ref="D116">Common_SourceData.Common_SourceData_RainfallZones_Source()</f>
@@ -18148,7 +18103,7 @@
       </c>
       <c r="BN116" s="22"/>
     </row>
-    <row r="117" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117"/>
       <c r="D117" s="26" t="str" cm="1">
         <f t="array" ref="D117">"⚠️" &amp; Common_SourceData.Common_SourceData_RainfallZones_Variation()</f>
@@ -18156,11 +18111,11 @@
       </c>
       <c r="BN117" s="22"/>
     </row>
-    <row r="118" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118"/>
       <c r="BN118" s="22"/>
     </row>
-    <row r="119" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119"/>
       <c r="D119" s="20" t="s">
         <v>52</v>
@@ -18176,7 +18131,7 @@
       </c>
       <c r="BN119" s="22"/>
     </row>
-    <row r="120" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120"/>
       <c r="D120" s="20" t="str" cm="1">
         <f t="array" ref="D120">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18196,7 +18151,7 @@
       </c>
       <c r="BN120" s="22"/>
     </row>
-    <row r="121" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121"/>
       <c r="D121" s="20" t="str" cm="1">
         <f t="array" ref="D121">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_RainfallZones_Data(),Table_SourceData_RainfallZones[[#Headers],[Rainfall Zone]],0)</f>
@@ -18216,31 +18171,31 @@
       </c>
       <c r="BN121" s="22"/>
     </row>
-    <row r="122" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122"/>
       <c r="BN122" s="22"/>
     </row>
-    <row r="123" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123"/>
     </row>
-    <row r="124" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124"/>
       <c r="D124" s="2" t="str" cm="1">
         <f t="array" ref="D124">Common_SourceData.Common_SourceData_LeachingZones_Title()</f>
         <v>VEERG Australian leaching zones</v>
       </c>
     </row>
-    <row r="125" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125"/>
       <c r="D125" s="18" t="str" cm="1">
         <f t="array" ref="D125">Common_SourceData.Common_SourceData_LeachingZones_Source()</f>
         <v>VEERG 2026: Table 1.3: Climate and Rainfall zone classifications and definitions</v>
       </c>
     </row>
-    <row r="126" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126"/>
     </row>
-    <row r="127" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127"/>
       <c r="D127" s="20" t="s">
         <v>54</v>
@@ -18249,7 +18204,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="128" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128"/>
       <c r="D128" s="20" t="str" cm="1">
         <f t="array" ref="D128">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18260,7 +18215,7 @@
         <v>Σ(𝑟𝑎𝑖𝑛)&gt;Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="129" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129"/>
       <c r="D129" s="20" t="str" cm="1">
         <f t="array" ref="D129">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_LeachingZones_Data(), Table_SourceData_LeachingZones[[#Headers],[Leaching Zone]], 0)</f>
@@ -18271,13 +18226,13 @@
         <v>Σ(𝑟𝑎𝑖𝑛)≤Σ(𝐸𝑇0)+𝑠𝑜𝑖𝑙 𝑤𝑎𝑡𝑒𝑟 ℎ𝑜𝑙𝑑𝑖𝑛𝑔 𝑐𝑎𝑝𝑎𝑐𝑖𝑡𝑦</v>
       </c>
     </row>
-    <row r="130" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130"/>
     </row>
-    <row r="131" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131"/>
     </row>
-    <row r="132" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132"/>
       <c r="D132" s="2" t="str" cm="1">
         <f t="array" ref="D132">Common_SourceData.Common_SourceData_FracWET_Title()</f>
@@ -18285,7 +18240,7 @@
       </c>
       <c r="E132" s="9"/>
     </row>
-    <row r="133" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133"/>
       <c r="D133" s="18" t="str" cm="1">
         <f t="array" ref="D133">Common_SourceData.Common_SourceData_FracWET_Source()</f>
@@ -18293,7 +18248,7 @@
       </c>
       <c r="E133" s="9"/>
     </row>
-    <row r="134" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134"/>
       <c r="D134" t="s">
         <v>56</v>
@@ -18302,7 +18257,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135"/>
       <c r="D135" t="str" cm="1">
         <f t="array" ref="D135">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18313,7 +18268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136"/>
       <c r="D136" s="1" t="str" cm="1">
         <f t="array" ref="D136">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWET_Data(),Table_SourceData_FracWET[[#Headers],[Is in leaching zone]],0)</f>
@@ -18324,10 +18279,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137"/>
     </row>
-    <row r="138" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138"/>
       <c r="BN138" s="22"/>
       <c r="BO138" s="22"/>
@@ -18342,7 +18297,7 @@
       <c r="BX138" s="22"/>
       <c r="BY138" s="22"/>
     </row>
-    <row r="139" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139"/>
       <c r="D139" s="2" t="str" cm="1">
         <f t="array" ref="D139">Common_SourceData.Common_SourceData_FracWETIrrigation_Title()</f>
@@ -18361,7 +18316,7 @@
       <c r="BX139" s="22"/>
       <c r="BY139" s="22"/>
     </row>
-    <row r="140" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140"/>
       <c r="D140" s="18" t="str" cm="1">
         <f t="array" ref="D140">Common_SourceData.Common_SourceData_FracWETIrrigation_Source()</f>
@@ -18380,7 +18335,7 @@
       <c r="BX140" s="22"/>
       <c r="BY140" s="22"/>
     </row>
-    <row r="141" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141"/>
       <c r="D141" s="26" t="str" cm="1">
         <f t="array" ref="D141">Common_SourceData.Common_SourceData_FracWETIrrigation_Variation()</f>
@@ -18388,7 +18343,7 @@
       </c>
       <c r="BN141" s="22"/>
     </row>
-    <row r="142" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142"/>
       <c r="D142" s="20" t="s">
         <v>58</v>
@@ -18398,7 +18353,7 @@
       </c>
       <c r="BN142" s="22"/>
     </row>
-    <row r="143" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143"/>
       <c r="D143" s="20" t="str" cm="1">
         <f t="array" ref="D143">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18410,7 +18365,7 @@
       </c>
       <c r="BN143" s="22"/>
     </row>
-    <row r="144" spans="1:77" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:77" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144"/>
       <c r="D144" s="1" t="str" cm="1">
         <f t="array" ref="D144">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18422,7 +18377,7 @@
       </c>
       <c r="BN144" s="22"/>
     </row>
-    <row r="145" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145"/>
       <c r="D145" s="1" t="str" cm="1">
         <f t="array" ref="D145">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18434,7 +18389,7 @@
       </c>
       <c r="BN145" s="22"/>
     </row>
-    <row r="146" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146"/>
       <c r="D146" s="1" t="str" cm="1">
         <f t="array" ref="D146">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18446,7 +18401,7 @@
       </c>
       <c r="BN146" s="22"/>
     </row>
-    <row r="147" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147"/>
       <c r="D147" s="1" t="str" cm="1">
         <f t="array" ref="D147">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_FracWETIrrigation_Data(), Table_SourceData_FracWETIrrigation[[#Headers],[Irrigation type i]], 0)</f>
@@ -18458,15 +18413,15 @@
       </c>
       <c r="BN147" s="22"/>
     </row>
-    <row r="148" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148"/>
       <c r="BN148" s="22"/>
     </row>
-    <row r="149" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149"/>
       <c r="BN149" s="22"/>
     </row>
-    <row r="150" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150"/>
       <c r="D150" s="2" t="str" cm="1">
         <f t="array" ref="D150">Common_SourceData.Common_SourceData_DataScores_Scope3_Title()</f>
@@ -18474,7 +18429,7 @@
       </c>
       <c r="BN150" s="22"/>
     </row>
-    <row r="151" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151"/>
       <c r="D151" s="18" t="str" cm="1">
         <f t="array" ref="D151">Common_SourceData.Common_SourceData_DataScores_Scope3_Source()</f>
@@ -18482,11 +18437,11 @@
       </c>
       <c r="BN151" s="22"/>
     </row>
-    <row r="152" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152"/>
       <c r="BN152" s="22"/>
     </row>
-    <row r="153" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153"/>
       <c r="D153" s="20" t="s">
         <v>59</v>
@@ -18506,7 +18461,7 @@
       <c r="BL153" s="25"/>
       <c r="BM153" s="25"/>
     </row>
-    <row r="154" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154"/>
       <c r="D154" s="20" t="str" cm="1">
         <f t="array" ref="D154">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18528,7 +18483,7 @@
       <c r="BL154" s="25"/>
       <c r="BM154" s="25"/>
     </row>
-    <row r="155" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155"/>
       <c r="D155" s="20" t="str" cm="1">
         <f t="array" ref="D155">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18550,7 +18505,7 @@
       <c r="BL155" s="25"/>
       <c r="BM155" s="25"/>
     </row>
-    <row r="156" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156"/>
       <c r="D156" s="20" t="str" cm="1">
         <f t="array" ref="D156">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18561,7 +18516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="157" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157"/>
       <c r="D157" s="20" t="str" cm="1">
         <f t="array" ref="D157">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18572,7 +18527,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="158" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158"/>
       <c r="D158" s="20" t="str" cm="1">
         <f t="array" ref="D158">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_DataScores_Scope3_Data(), Table_SourceData_DataScores_Scope3[[#Headers],[Data source]], 0)</f>
@@ -18583,34 +18538,34 @@
         <v>5</v>
       </c>
     </row>
-    <row r="159" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159"/>
     </row>
-    <row r="160" spans="1:66" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:66" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160"/>
     </row>
-    <row r="161" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D161" s="2" t="str" cm="1">
         <f t="array" ref="D161">Common_SourceData.Common_SourceData_FracLEACH_Title()</f>
         <v>Fraction of N that is available for leaching and runoff</v>
       </c>
       <c r="E161" s="9"/>
     </row>
-    <row r="162" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D162" s="18" t="str" cm="1">
         <f t="array" ref="D162">Common_SourceData.Common_SourceData_FracLEACH_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
       </c>
       <c r="E162" s="9"/>
     </row>
-    <row r="163" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D163" s="18" t="str" cm="1">
         <f t="array" ref="D163">Common_SourceData.Common_SourceData_FracLEACH_NIRReference()</f>
         <v>National Inventory Report Volume 1: Leaching and runoff (3.D.b.2)</v>
       </c>
       <c r="E163" s="9"/>
     </row>
-    <row r="164" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D164" s="9" t="str" cm="1">
         <f t="array" ref="D164:E164">Common_SourceData.Common_SourceData_FracLEACH_Data()</f>
         <v>FracLEACH</v>
@@ -18619,17 +18574,17 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="165" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN165" s="22"/>
       <c r="BO165" s="22"/>
       <c r="BP165" s="22"/>
     </row>
-    <row r="166" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN166" s="22"/>
       <c r="BO166" s="22"/>
       <c r="BP166" s="22"/>
     </row>
-    <row r="167" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D167" s="2" t="str" cm="1">
         <f t="array" ref="D167">Common_SourceData.Common_SourceData_EFleach_Title()</f>
         <v>Emission factor for nitrogen leaching and runoff</v>
@@ -18638,7 +18593,7 @@
       <c r="BO167" s="22"/>
       <c r="BP167" s="22"/>
     </row>
-    <row r="168" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D168" s="18" t="str" cm="1">
         <f t="array" ref="D168">Common_SourceData.Common_SourceData_EFleach_Source()</f>
         <v>VEERG 2026:5.5.2.3 Constant Parameters</v>
@@ -18647,7 +18602,7 @@
       <c r="BO168" s="22"/>
       <c r="BP168" s="22"/>
     </row>
-    <row r="169" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D169" s="18" t="str" cm="1">
         <f t="array" ref="D169">Common_SourceData.Common_SourceData_EFleach_NIRReference()</f>
         <v>National Inventory Report Volume 1: Equation 3.D.B_10</v>
@@ -18656,7 +18611,7 @@
       <c r="BO169" s="22"/>
       <c r="BP169" s="22"/>
     </row>
-    <row r="170" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D170" s="1" t="str" cm="1">
         <f t="array" ref="D170:E170">Common_SourceData.Common_SourceData_EFleach_Data()</f>
         <v>EFleach</v>
@@ -18668,17 +18623,17 @@
       <c r="BO170" s="22"/>
       <c r="BP170" s="22"/>
     </row>
-    <row r="171" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN171" s="22"/>
       <c r="BO171" s="22"/>
       <c r="BP171" s="22"/>
     </row>
-    <row r="172" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN172" s="22"/>
       <c r="BO172" s="22"/>
       <c r="BP172" s="22"/>
     </row>
-    <row r="173" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D173" s="2" t="str" cm="1">
         <f t="array" ref="D173">Common_SourceData.Common_SourceData_DensityOfMethane_Title()</f>
         <v>p = density of methane</v>
@@ -18687,7 +18642,7 @@
       <c r="BO173" s="22"/>
       <c r="BP173" s="22"/>
     </row>
-    <row r="174" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D174" s="18" t="str" cm="1">
         <f t="array" ref="D174">Common_SourceData.Common_SourceData_DensityOfMethane_Source()</f>
         <v>National Inventory Report 2023 Volume 1: Equations 3.B.1a_2, 3.B.1c_2, 3.B.3_1, 3.B.4g_2</v>
@@ -18696,7 +18651,7 @@
       <c r="BO174" s="22"/>
       <c r="BP174" s="22"/>
     </row>
-    <row r="175" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D175" s="1" cm="1">
         <f t="array" ref="D175">Common_SourceData.Common_SourceData_DensityOfMethane_Data()</f>
         <v>0.6784</v>
@@ -18709,17 +18664,17 @@
       <c r="BO175" s="22"/>
       <c r="BP175" s="22"/>
     </row>
-    <row r="176" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN176" s="22"/>
       <c r="BO176" s="22"/>
       <c r="BP176" s="22"/>
     </row>
-    <row r="177" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="BN177" s="22"/>
       <c r="BO177" s="22"/>
       <c r="BP177" s="22"/>
     </row>
-    <row r="178" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D178" s="2" t="str" cm="1">
         <f t="array" ref="D178">Common_SourceData.Common_SourceData_EFN2O_Title()</f>
         <v>Nitrous oxide emission factors for inorganic fertiliser application</v>
@@ -18728,7 +18683,7 @@
       <c r="BO178" s="22"/>
       <c r="BP178" s="22"/>
     </row>
-    <row r="179" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D179" s="18" t="str" cm="1">
         <f t="array" ref="D179">Common_SourceData.Common_SourceData_EFN2O_Source()</f>
         <v>VEERG 2026: Table A.2.2.1</v>
@@ -18737,39 +18692,39 @@
       <c r="BO179" s="22"/>
       <c r="BP179" s="22"/>
     </row>
-    <row r="180" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D180" s="10" t="str" cm="1">
         <f t="array" ref="D180">Common_SourceData.Common_SourceData_EFN2O_Unit()</f>
         <v>(kg N2O-N / kg N</v>
       </c>
     </row>
-    <row r="181" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D181" s="26" t="str" cm="1">
         <f t="array" ref="D181:D185">Common_SourceData.Common_SourceData_EFN2O_Variation()</f>
         <v>VARIATION OF SOURCE DATA:</v>
       </c>
     </row>
-    <row r="182" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D182" s="26" t="str">
         <v>Removed duplicate 'Aquaculture' row.</v>
       </c>
     </row>
-    <row r="183" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D183" s="26" t="str">
         <v>Removed asterisks to aid lookup.</v>
       </c>
     </row>
-    <row r="184" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D184" s="26" t="str">
         <v>Added 'production system only', 'rainfall zone' and 'irrigation method' columns to aid lookup.</v>
       </c>
     </row>
-    <row r="185" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D185" s="26" t="str">
         <v>Duplicated 'non-irrigated pasture' row with same EF for low and high rainfall zones to aid lookup.</v>
       </c>
     </row>
-    <row r="186" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D186" s="20" t="s">
         <v>61</v>
       </c>
@@ -18786,7 +18741,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="187" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D187" s="20" t="str" cm="1">
         <f t="array" ref="D187">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated pasture</v>
@@ -18808,7 +18763,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="188" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D188" s="20" t="str" cm="1">
         <f t="array" ref="D188">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Irrigated crop</v>
@@ -18830,7 +18785,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="189" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D189" s="20" t="str" cm="1">
         <f t="array" ref="D189">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18852,7 +18807,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="190" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D190" s="20" t="str" cm="1">
         <f t="array" ref="D190">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated pasture</v>
@@ -18874,7 +18829,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="191" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D191" s="20" t="str" cm="1">
         <f t="array" ref="D191">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (low rainfall)</v>
@@ -18896,7 +18851,7 @@
         <v>Low rainfall</v>
       </c>
     </row>
-    <row r="192" spans="4:68" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:68" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D192" s="20" t="str" cm="1">
         <f t="array" ref="D192">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Non-irrigated crop (high rainfall)</v>
@@ -18918,7 +18873,7 @@
         <v>High rainfall</v>
       </c>
     </row>
-    <row r="193" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D193" s="20" t="str" cm="1">
         <f t="array" ref="D193">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Sugar</v>
@@ -18940,7 +18895,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="194" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D194" s="20" t="str" cm="1">
         <f t="array" ref="D194">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Cotton</v>
@@ -18962,7 +18917,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="195" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D195" s="20" t="str" cm="1">
         <f t="array" ref="D195">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Horticultural crops</v>
@@ -18984,7 +18939,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="196" spans="4:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:8" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D196" s="20" t="str" cm="1">
         <f t="array" ref="D196">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (continuous flooding)</v>
@@ -19006,7 +18961,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="197" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D197" s="20" t="str" cm="1">
         <f t="array" ref="D197">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Rice (single and multiple drainage, or alternate wetting and drying)</v>
@@ -19028,7 +18983,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="198" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D198" s="20" t="str" cm="1">
         <f t="array" ref="D198">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Aquaculture</v>
@@ -19050,7 +19005,7 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="199" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D199" s="20" t="str" cm="1">
         <f t="array" ref="D199">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFN2O_Data(), Table_SourceData_Common_EFN2O[[#Headers],[Production system j]], 0)</f>
         <v>Forestry</v>
@@ -19072,31 +19027,31 @@
         <v>Any</v>
       </c>
     </row>
-    <row r="202" spans="4:8" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:8" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D202" s="2" t="str" cm="1">
         <f t="array" ref="D202">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Title()</f>
         <v>Emission factor for urine and dung deposited on pasture, range or paddock</v>
       </c>
     </row>
-    <row r="203" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D203" s="18" t="str" cm="1">
         <f t="array" ref="D203">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Source()</f>
         <v>VEERG 2026: Table A.2.2.2</v>
       </c>
     </row>
-    <row r="204" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D204" s="26" t="str" cm="1">
         <f t="array" ref="D204">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Variation()</f>
         <v>VARIATION FROM SOURCE DATA: Changed 'Dry climate zones' to singular 'Dry climate zone' to aid lookup.</v>
       </c>
     </row>
-    <row r="205" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D205" s="10" t="str" cm="1">
         <f t="array" ref="D205">Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="206" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D206" s="20" t="s">
         <v>32</v>
       </c>
@@ -19104,7 +19059,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="207" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D207" s="20" t="str" cm="1">
         <f t="array" ref="D207">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -19114,7 +19069,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="208" spans="4:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:8" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D208" s="1" t="str" cm="1">
         <f t="array" ref="D208">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFPastureRangeAndPaddock_Data(), Table_SourceData_EFPastureRangeAndPaddock[[#Headers],[Climate zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -19124,13 +19079,13 @@
         <v>2E-3</v>
       </c>
     </row>
-    <row r="211" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D211" s="1" t="str" cm="1">
         <f t="array" ref="D211">Common_SourceData.Common_SourceData_MonthsToSeasons_Title()</f>
         <v>Months to Seasons Mapping</v>
       </c>
     </row>
-    <row r="212" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D212" s="20" t="s">
         <v>67</v>
       </c>
@@ -19138,7 +19093,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="213" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D213" s="20" t="str" cm="1">
         <f t="array" ref="D213">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>January</v>
@@ -19148,7 +19103,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="214" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D214" s="1" t="str" cm="1">
         <f t="array" ref="D214">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>February</v>
@@ -19158,7 +19113,7 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="215" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D215" s="1" t="str" cm="1">
         <f t="array" ref="D215">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>March</v>
@@ -19168,7 +19123,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="216" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D216" s="1" t="str" cm="1">
         <f t="array" ref="D216">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>April</v>
@@ -19178,7 +19133,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="217" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D217" s="1" t="str" cm="1">
         <f t="array" ref="D217">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>May</v>
@@ -19188,7 +19143,7 @@
         <v>Autumn</v>
       </c>
     </row>
-    <row r="218" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D218" s="1" t="str" cm="1">
         <f t="array" ref="D218">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>June</v>
@@ -19198,7 +19153,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="219" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D219" s="1" t="str" cm="1">
         <f t="array" ref="D219">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>July</v>
@@ -19208,7 +19163,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="220" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D220" s="1" t="str" cm="1">
         <f t="array" ref="D220">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>August</v>
@@ -19218,7 +19173,7 @@
         <v>Winter</v>
       </c>
     </row>
-    <row r="221" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D221" s="1" t="str" cm="1">
         <f t="array" ref="D221">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>September</v>
@@ -19228,7 +19183,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="222" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D222" s="1" t="str" cm="1">
         <f t="array" ref="D222">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>October</v>
@@ -19238,7 +19193,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="223" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D223" s="1" t="str" cm="1">
         <f t="array" ref="D223">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>November</v>
@@ -19248,7 +19203,7 @@
         <v>Spring</v>
       </c>
     </row>
-    <row r="224" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:5" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D224" s="1" t="str" cm="1">
         <f t="array" ref="D224">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MonthsToSeasons_Data(), Table_SourceData_Common_MonthToSeason[[#Headers],[Month]], 0)</f>
         <v>December</v>
@@ -19258,25 +19213,25 @@
         <v>Summer</v>
       </c>
     </row>
-    <row r="227" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D227" s="2" t="str" cm="1">
         <f t="array" ref="D227">Common_SourceData.Common_SourceData_MCFTemperatureZone_Title()</f>
         <v>Manure Management – Methane conversion factor per temperature zone (fraction) (MCFim)</v>
       </c>
     </row>
-    <row r="228" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D228" s="18" t="str" cm="1">
         <f t="array" ref="D228">Common_SourceData.Common_SourceData_MCFTemperatureZone_Source()</f>
         <v>VEERG 2026: Table A.1.8.1</v>
       </c>
     </row>
-    <row r="229" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D229" s="26" t="str" cm="1">
         <f t="array" ref="D229">Common_SourceData.Common_SourceData_MCFTemperatureZone_Variation()</f>
         <v>VARIATION FROM SOURCE: Added row of NIR MMA definitions to aid lookup. Duplicated 'Poultry with and without litter' column with separate NIR definitions to aid lookup. Added 'MAT raw' column to allow lookup of numbers.</v>
       </c>
     </row>
-    <row r="231" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D231" s="20" t="s">
         <v>69</v>
       </c>
@@ -19326,7 +19281,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="232" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D232" s="20" t="str" cm="1">
         <f t="array" ref="D232">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19392,7 +19347,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D233" s="1" t="str" cm="1">
         <f t="array" ref="D233">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19458,7 +19413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="234" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D234" s="1" t="str" cm="1">
         <f t="array" ref="D234">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19524,7 +19479,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="235" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D235" s="1" t="str" cm="1">
         <f t="array" ref="D235">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19590,7 +19545,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="236" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D236" s="1" t="str" cm="1">
         <f t="array" ref="D236">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Cool</v>
@@ -19656,7 +19611,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="237" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D237" s="1" t="str" cm="1">
         <f t="array" ref="D237">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19722,7 +19677,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="238" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D238" s="1" t="str" cm="1">
         <f t="array" ref="D238">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19788,7 +19743,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="239" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D239" s="1" t="str" cm="1">
         <f t="array" ref="D239">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19854,7 +19809,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="240" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D240" s="1" t="str" cm="1">
         <f t="array" ref="D240">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19920,7 +19875,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="241" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D241" s="1" t="str" cm="1">
         <f t="array" ref="D241">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -19986,7 +19941,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="242" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D242" s="1" t="str" cm="1">
         <f t="array" ref="D242">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20052,7 +20007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="243" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D243" s="1" t="str" cm="1">
         <f t="array" ref="D243">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20118,7 +20073,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="244" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D244" s="1" t="str" cm="1">
         <f t="array" ref="D244">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20184,7 +20139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D245" s="1" t="str" cm="1">
         <f t="array" ref="D245">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20250,7 +20205,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="246" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D246" s="1" t="str" cm="1">
         <f t="array" ref="D246">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20316,7 +20271,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="247" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D247" s="1" t="str" cm="1">
         <f t="array" ref="D247">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Temperate</v>
@@ -20382,7 +20337,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="248" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D248" s="1" t="str" cm="1">
         <f t="array" ref="D248">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20448,7 +20403,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="249" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D249" s="1" t="str" cm="1">
         <f t="array" ref="D249">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20514,7 +20469,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="250" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D250" s="1" t="str" cm="1">
         <f t="array" ref="D250">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_MCFTemperatureZone_Data(),Table_SourceData_Common_MCFTemperatureZone[[#Headers],[Temperature zone]],0)</f>
         <v>Warm</v>
@@ -20580,31 +20535,31 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253" spans="4:19" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:19" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D253" s="2" t="str" cm="1">
         <f t="array" ref="D253">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Title()</f>
         <v>Emission factor for organic fertiliser and crop residues returned to the soil</v>
       </c>
     </row>
-    <row r="254" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D254" s="18" t="str" cm="1">
         <f t="array" ref="D254">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Source()</f>
         <v>VEERG 2026: Table A.2.1.4</v>
       </c>
     </row>
-    <row r="255" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D255" s="1" t="str" cm="1">
         <f t="array" ref="D255">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Variable()</f>
         <v>EFNi &amp; EFN2Oi</v>
       </c>
     </row>
-    <row r="256" spans="4:19" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:19" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D256" s="10" t="str" cm="1">
         <f t="array" ref="D256">Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Unit()</f>
         <v>kg N2O - N / kg N</v>
       </c>
     </row>
-    <row r="257" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D257" s="20" t="s">
         <v>85</v>
       </c>
@@ -20612,7 +20567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="258" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D258" s="20" t="str" cm="1">
         <f t="array" ref="D258">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Wet climate zone</v>
@@ -20622,7 +20577,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="259" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D259" s="1" t="str" cm="1">
         <f t="array" ref="D259">Common_InputFunctions.Utility_DisplayArrayInTable(Common_SourceData.Common_SourceData_EFOrganicFertiliserAndCropResidues_Data(), Table_SourceData_Common_EFOrganicFertCropResidues[[#Headers],[Climate Zone]], 0)</f>
         <v>Dry climate zone</v>
@@ -20632,17 +20587,17 @@
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="263" spans="4:66" ht="23.25" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:66" ht="20" x14ac:dyDescent="0.25" customHeight="1">
       <c r="D263" s="2" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="264" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D264" s="1" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="265" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D265" s="20" t="s">
         <v>199</v>
       </c>
@@ -20658,7 +20613,7 @@
       <c r="V265" s="1"/>
       <c r="BN265" s="22"/>
     </row>
-    <row r="266" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D266" s="20" t="s">
         <v>200</v>
       </c>
@@ -20674,7 +20629,7 @@
       <c r="V266" s="1"/>
       <c r="BN266" s="22"/>
     </row>
-    <row r="267" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D267" s="20" t="s">
         <v>201</v>
       </c>
@@ -20690,7 +20645,7 @@
       <c r="V267" s="1"/>
       <c r="BN267" s="22"/>
     </row>
-    <row r="268" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D268" s="20" t="s">
         <v>202</v>
       </c>
@@ -20706,7 +20661,7 @@
       <c r="V268" s="1"/>
       <c r="BN268" s="22"/>
     </row>
-    <row r="269" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D269" s="20" t="s">
         <v>203</v>
       </c>
@@ -20722,7 +20677,7 @@
       <c r="V269" s="1"/>
       <c r="BN269" s="22"/>
     </row>
-    <row r="270" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D270" s="20" t="s">
         <v>204</v>
       </c>
@@ -20738,12 +20693,12 @@
       <c r="V270" s="1"/>
       <c r="BN270" s="22"/>
     </row>
-    <row r="273" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D273" s="1" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="274" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D274" s="20" t="s">
         <v>199</v>
       </c>
@@ -20759,7 +20714,7 @@
       <c r="V274" s="1"/>
       <c r="BN274" s="22"/>
     </row>
-    <row r="275" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D275" s="20" t="s">
         <v>205</v>
       </c>
@@ -20775,7 +20730,7 @@
       <c r="V275" s="1"/>
       <c r="BN275" s="22"/>
     </row>
-    <row r="276" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D276" s="20" t="s">
         <v>206</v>
       </c>
@@ -20791,7 +20746,7 @@
       <c r="V276" s="1"/>
       <c r="BN276" s="22"/>
     </row>
-    <row r="277" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D277" s="20" t="s">
         <v>207</v>
       </c>
@@ -20807,7 +20762,7 @@
       <c r="V277" s="1"/>
       <c r="BN277" s="22"/>
     </row>
-    <row r="278" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D278" s="20" t="s">
         <v>208</v>
       </c>
@@ -20823,7 +20778,7 @@
       <c r="V278" s="1"/>
       <c r="BN278" s="22"/>
     </row>
-    <row r="279" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D279" s="20" t="s">
         <v>209</v>
       </c>
@@ -20839,12 +20794,12 @@
       <c r="V279" s="1"/>
       <c r="BN279" s="22"/>
     </row>
-    <row r="282" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D282" s="1" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="283" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D283" s="20" t="s">
         <v>199</v>
       </c>
@@ -20860,7 +20815,7 @@
       <c r="V283" s="1"/>
       <c r="BN283" s="22"/>
     </row>
-    <row r="284" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D284" s="20" t="s">
         <v>210</v>
       </c>
@@ -20876,7 +20831,7 @@
       <c r="V284" s="1"/>
       <c r="BN284" s="22"/>
     </row>
-    <row r="285" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D285" s="20" t="s">
         <v>211</v>
       </c>
@@ -20892,7 +20847,7 @@
       <c r="V285" s="1"/>
       <c r="BN285" s="22"/>
     </row>
-    <row r="286" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D286" s="20" t="s">
         <v>212</v>
       </c>
@@ -20908,7 +20863,7 @@
       <c r="V286" s="1"/>
       <c r="BN286" s="22"/>
     </row>
-    <row r="287" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D287" s="20" t="s">
         <v>213</v>
       </c>
@@ -20924,7 +20879,7 @@
       <c r="V287" s="1"/>
       <c r="BN287" s="22"/>
     </row>
-    <row r="288" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D288" s="20" t="s">
         <v>214</v>
       </c>
@@ -20940,12 +20895,12 @@
       <c r="V288" s="1"/>
       <c r="BN288" s="22"/>
     </row>
-    <row r="291" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D291" s="1" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="292" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D292" s="20" t="s">
         <v>199</v>
       </c>
@@ -20961,7 +20916,7 @@
       <c r="V292" s="1"/>
       <c r="BN292" s="22"/>
     </row>
-    <row r="293" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D293" s="20" t="s">
         <v>215</v>
       </c>
@@ -20977,7 +20932,7 @@
       <c r="V293" s="1"/>
       <c r="BN293" s="22"/>
     </row>
-    <row r="294" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D294" s="20" t="s">
         <v>216</v>
       </c>
@@ -20993,7 +20948,7 @@
       <c r="V294" s="1"/>
       <c r="BN294" s="22"/>
     </row>
-    <row r="295" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D295" s="20" t="s">
         <v>217</v>
       </c>
@@ -21009,7 +20964,7 @@
       <c r="V295" s="1"/>
       <c r="BN295" s="22"/>
     </row>
-    <row r="296" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D296" s="20" t="s">
         <v>218</v>
       </c>
@@ -21025,7 +20980,7 @@
       <c r="V296" s="1"/>
       <c r="BN296" s="22"/>
     </row>
-    <row r="297" spans="4:66" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:66" x14ac:dyDescent="0.25" ht="20" customHeight="1">
       <c r="D297" s="20" t="s">
         <v>219</v>
       </c>
